--- a/results/cluster_ga/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
@@ -657,22 +657,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.55219795951094</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.92237946731601</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.4288540889339</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.29270580000829</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.65816502564173</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.63508616180749</v>
+        <v>26.08541819849162</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.98528890066206</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.95117069352023</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.5313765696454</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.6456021765115</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.04044378793501</v>
       </c>
     </row>
   </sheetData>
@@ -731,22 +731,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.8817080920566</v>
-      </c>
-      <c r="C2" t="n">
-        <v>61.34349152068996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.3980435658566</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.99199137124974</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.83258654564217</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.99853580533711</v>
+        <v>30.81327585454991</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.18209182292396</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.18465442381298</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.5520270427433</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.16423687396098</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.51999470387581</v>
       </c>
     </row>
   </sheetData>
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.70810624588173</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.42385470348707</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.30913136481186</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.44968899439117</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.10115670059908</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.35048521321504</v>
+        <v>27.41312294393639</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.38925396378113</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.03754351293132</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.38772742458494</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.19350376837788</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.63227880125322</v>
       </c>
     </row>
   </sheetData>
@@ -879,22 +879,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.64588702808297</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.36960333806237</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.65786493777888</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.18595704767269</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.09842838439172</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.50386790576291</v>
+        <v>32.60136688251971</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.02462057059741</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.47994099926488</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.91111448592255</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.04760836361103</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.02525272881275</v>
       </c>
     </row>
   </sheetData>
@@ -953,22 +953,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.0940371586523</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.44400177577903</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.59741633240893</v>
-      </c>
-      <c r="E2" t="n">
-        <v>51.53505824269448</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.81344158430232</v>
-      </c>
-      <c r="G2" t="n">
-        <v>21.31827306664668</v>
+        <v>32.85748187456914</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.06808223805803</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.75261304869947</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.22125797313405</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.92902728913585</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.07552765235396</v>
       </c>
     </row>
   </sheetData>
@@ -1027,22 +1027,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.93321879689044</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.4702735719267</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.37633883283755</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.67978475760433</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.02568895208022</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.85417810176875</v>
+        <v>30.81041485980475</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.86942084874754</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.75256615372334</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.72707413609201</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.29695978076811</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.80719558919131</v>
       </c>
     </row>
   </sheetData>
@@ -1101,22 +1101,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.00006350734142</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.27379448902051</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.361127326304</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.04508337352866</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.19291032857637</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.77150410796674</v>
+        <v>26.01761018163163</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.34243983485961</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.68660910743692</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.58709590477333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.18131503255106</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.37400838991197</v>
       </c>
     </row>
   </sheetData>
@@ -1175,22 +1175,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.32783737825309</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.86615029731706</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.44727160846035</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.01344781867265</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.06020396923919</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.02107295139447</v>
+        <v>32.85353243732421</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.55750741650719</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.97412580719715</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.73103162344123</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.22673135674131</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.72440976529158</v>
       </c>
     </row>
   </sheetData>
@@ -1249,22 +1249,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.51938492579189</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.80091710908934</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.77169453390328</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.47047203956795</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.90463893667997</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.97523196661726</v>
+        <v>36.94483621052103</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.7640572622196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.46644537934781</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.39423535467614</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.33978509344982</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.35209341806849</v>
       </c>
     </row>
   </sheetData>
@@ -1323,22 +1323,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.04529594213536</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.75588406869243</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.19360232451275</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.7447541848578</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.03838839836144</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.93996530879622</v>
+        <v>23.68970240758218</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.29240509666241</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.22060879991641</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.01569608085543</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.46650960250147</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.38693006946929</v>
       </c>
     </row>
   </sheetData>
@@ -1397,22 +1397,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.5036405466926</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.57269017013938</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.31535858207566</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.85123666031131</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.67757613553472</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.79231673146144</v>
+        <v>27.37859668526741</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.7257940066344</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.47258756544977</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.80150777341134</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.82981720611932</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.94807903475966</v>
       </c>
     </row>
   </sheetData>
@@ -1471,22 +1471,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.32836434571182</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.75634763304306</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.01952656959246</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.14787369591198</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.45348146528729</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.29617103603096</v>
+        <v>30.16595374376585</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.22430905154766</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.13611900757557</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.39643983148162</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.34305229568677</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.56567051531788</v>
       </c>
     </row>
   </sheetData>
@@ -1545,22 +1545,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.87513913291717</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.23864935923269</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.39572087537315</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.97080656712395</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.91048275703437</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.487289767173</v>
+        <v>25.16292761428067</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.33089903414259</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.01216560385143</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.24635950264695</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.96544984342292</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.44120718408546</v>
       </c>
     </row>
   </sheetData>
@@ -1619,22 +1619,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.52331069093343</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.45502186905591</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.9877273871384</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.04498306062213</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.71410868893607</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.84048521399948</v>
+        <v>35.16877776744726</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.65566438718453</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.21910053150017</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.79289327772644</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.221987425189</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.34904029747084</v>
       </c>
     </row>
   </sheetData>
@@ -1693,22 +1693,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.92586205476952</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.24187574447707</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.31189400859324</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.31399301700991</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.02244544849205</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.12608083155489</v>
+        <v>29.97001090011808</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.98682831394159</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.65220554143407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.84317208180362</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.57395702663291</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.90179660370741</v>
       </c>
     </row>
   </sheetData>
@@ -1767,22 +1767,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.40214630075749</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.96352215703393</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.3841140123781</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.14295751306157</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.85465582258562</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.05189279066233</v>
+        <v>25.94536002916978</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.5561422822081</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.02504064927591</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.58453176378563</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.05030936581225</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.04076817566771</v>
       </c>
     </row>
   </sheetData>
@@ -1841,22 +1841,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.19862466681462</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.27820325488989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.7563027041343</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.51072748277022</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.06866150663585</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.35850451855086</v>
+        <v>36.61295141270322</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.88236756934304</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.04839631373977</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.44438346064491</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.81698011852068</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.99105830780575</v>
       </c>
     </row>
   </sheetData>
@@ -1915,22 +1915,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.20676104422136</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.60908338141338</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.01675670371248</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.99051605126787</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.44149468187075</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.82431283500612</v>
+        <v>28.37901583809413</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.00305354454139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.49491942338958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.32130661521551</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.3681109463412</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.54163421533541</v>
       </c>
     </row>
   </sheetData>
@@ -1989,22 +1989,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.20064859344949</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.97562084776695</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.3216437237926</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.107013388123</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.62643844823619</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.33115810888849</v>
+        <v>43.2466957239533</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.62143532396149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.64064082234067</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.59577118242607</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.90289257604874</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.74159062555689</v>
       </c>
     </row>
   </sheetData>
@@ -2063,22 +2063,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.82819276038544</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.14003424879623</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.01171675148125</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.80334137532892</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.26732140549628</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.88134353765228</v>
+        <v>25.86813749683888</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.33317978404921</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.58101846116531</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.59878772932413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.38365318154559</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.44556562585741</v>
       </c>
     </row>
   </sheetData>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.91984401335266</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.72605796680183</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.44301193359145</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.33890525498797</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.01667354952449</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.67550304675419</v>
+        <v>30.0515594079114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.94808815268225</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.45697770191752</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.96178510796332</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.19791025154542</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.97010318492423</v>
       </c>
     </row>
   </sheetData>
@@ -2211,22 +2211,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.26862460242712</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.78654792568058</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.04120910011035</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.33404205817261</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.30797646861203</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.54433841245331</v>
+        <v>28.57774516688177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.7136187178802</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.695879428211</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.29521398561808</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.03400819434489</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.88512271667447</v>
       </c>
     </row>
   </sheetData>
@@ -2285,22 +2285,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.63235742042369</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.86011612142801</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.84490864264508</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.51070570671143</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.36940590945942</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.90811979367037</v>
+        <v>31.67434298226899</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.50315075041607</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.16062654396906</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.65978026341411</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.53230177667606</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.6662922828203</v>
       </c>
     </row>
   </sheetData>
@@ -2359,22 +2359,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.88513684901952</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.67039761262694</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.16988006296354</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.07768911823713</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.06172083919997</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.54707379062091</v>
+        <v>32.12742890873314</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.82499303226866</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.84746591154238</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.5045056084106</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.77152223199455</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.08794577153295</v>
       </c>
     </row>
   </sheetData>
@@ -2433,22 +2433,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.61534376544972</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.51268507937654</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.14761442802142</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.52257991195843</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.79992645528268</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.05057607843536</v>
+        <v>24.7946884029392</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.34488302470817</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.26293975674842</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.95712139924993</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.65648442527586</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.45882651745434</v>
       </c>
     </row>
   </sheetData>
@@ -2507,22 +2507,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.05426538009271</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.21595387441251</v>
-      </c>
-      <c r="D2" t="n">
-        <v>14.28186596674216</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.32175589453036</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.59333364713034</v>
-      </c>
-      <c r="G2" t="n">
-        <v>63.05810961265005</v>
+        <v>31.0176921556151</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.51516786477622</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.91757478989648</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.36706528504658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.19146217153442</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.34131692510998</v>
       </c>
     </row>
   </sheetData>
@@ -2581,22 +2581,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.56687952921242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.4635033090976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.4672039450199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.13848791359246</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.49439984628126</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.38269998388555</v>
+        <v>28.95752663488058</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.99214146102322</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.04740007382991</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.84410865932207</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.40098221060979</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.05701927617793</v>
       </c>
     </row>
   </sheetData>
@@ -2655,22 +2655,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.58380898131238</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.44697119846361</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.27549450921074</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.58071029545305</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.80181632574363</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.69130966809655</v>
+        <v>32.09639146153275</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.2855575639517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.70239745873126</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.76942965098254</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.54615604616694</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.0880144719457</v>
       </c>
     </row>
   </sheetData>
@@ -2729,22 +2729,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.92325122752905</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.69268798214607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.13746971704871</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.33894580283877</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.15651726371538</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.48406627125149</v>
+        <v>23.70451012662148</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.68559244108865</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.73242339889112</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.93389073422858</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.65253828650382</v>
+      </c>
+      <c r="G2" t="n">
+        <v>61.30308041849641</v>
       </c>
     </row>
   </sheetData>
@@ -2803,22 +2803,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.1975275808939</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.28690999845254</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.44780832653195</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.07252412642258</v>
-      </c>
-      <c r="F2" t="n">
-        <v>19.32574966601918</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.26128042668923</v>
+        <v>30.38791263504713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.53787516108553</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.08761004874286</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.01143816416679</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.67540912241873</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.74708184228019</v>
       </c>
     </row>
   </sheetData>
@@ -2877,22 +2877,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.14580392896601</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.82860105506741</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.61234203886377</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.77234329330706</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.65673052070176</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.70991020573015</v>
+        <v>28.14315509143745</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.08231391572821</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.62876134774355</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.73530474556303</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.68835301533798</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.62196622035314</v>
       </c>
     </row>
   </sheetData>
@@ -2951,22 +2951,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.92589788345176</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.35281104777766</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.43213087022063</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.6585387429006</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.28657813691322</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.07453200159149</v>
+        <v>33.34378067097136</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.82687592979534</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.12693801968081</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.25607247305439</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.41818725997081</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.46525713218239</v>
       </c>
     </row>
   </sheetData>
@@ -3025,22 +3025,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.88676747111315</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50.12102077428403</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.73657582629696</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.29140762007742</v>
-      </c>
-      <c r="F2" t="n">
-        <v>19.93859348445109</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.8183431005553</v>
+        <v>30.88318930521924</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.53779922303432</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.76104431295344</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.95658116693208</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.68401550010197</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.62647825381575</v>
       </c>
     </row>
   </sheetData>
@@ -3099,22 +3099,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.87819878229771</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.68264193593733</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.73347409076844</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.43166124114796</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.49158567735963</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.83527778812717</v>
+        <v>31.60793821287765</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.72144900719703</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.42150268090895</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.69293706875927</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.11348444536701</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.51992870594533</v>
       </c>
     </row>
   </sheetData>
@@ -3173,22 +3173,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.64714289637119</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.18549437854768</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.4913063901197</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.97395503396418</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.31150883649332</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.89533465017533</v>
+        <v>28.14109832849951</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.57042255532067</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.1423436916057</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.13325239327093</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.86523794681494</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.27967794281236</v>
       </c>
     </row>
   </sheetData>
@@ -3247,22 +3247,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.70937674827481</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.07497797795803</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.61500457808476</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.29799689544338</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.21323159238208</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.87230634078524</v>
+        <v>27.44516222214725</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.40970922750962</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.03217868131855</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.97826627297518</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.19544039554931</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.75664338075188</v>
       </c>
     </row>
   </sheetData>
@@ -3321,22 +3321,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.75369721177201</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.92423147331865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.16111991550198</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.45800519469166</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.75354124378071</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.54115820288663</v>
+        <v>30.7339381482131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.00124577784845</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.13646004951512</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.83358112384412</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.94557895659525</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.05704722882714</v>
       </c>
     </row>
   </sheetData>
@@ -3395,22 +3395,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.56003782653868</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.11105132883217</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.01391823903499</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.65485275872361</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18.09451166326194</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.66852090860251</v>
+        <v>32.62735862711305</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.73043073013215</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.7215162623275</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.68125774962555</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.18487863230706</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.57006217813694</v>
       </c>
     </row>
   </sheetData>
@@ -3469,22 +3469,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.7483977932828</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.64735110460234</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.89107835923774</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.93148513689949</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.69445040973649</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.11791279827266</v>
+        <v>34.97494889601055</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.62264468414833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.6571783263787</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.79237051760838</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.20943897737114</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.23843752743036</v>
       </c>
     </row>
   </sheetData>
@@ -3543,22 +3543,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.33742069901171</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.35581302103584</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.76185595846835</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.41196508100819</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.24708742297612</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.20426835878342</v>
+        <v>28.24019393125207</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.78027747187448</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.16293550793589</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.82788743007579</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.66017529084369</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.52953040660132</v>
       </c>
     </row>
   </sheetData>
@@ -3617,22 +3617,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.68612802963118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.30586129153319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.2781481149869</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.35905816404425</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.80316750294008</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.26679952594756</v>
+        <v>28.81477614655694</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.68515607585993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.30538331005132</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.62131686838803</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.20281845643776</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.11667123707639</v>
       </c>
     </row>
   </sheetData>
@@ -3691,22 +3691,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.72612144691346</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.34844792772519</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.47808904896972</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.05607993373224</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.94267031375124</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.49088004245583</v>
+        <v>37.43060259338354</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.18022419251021</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.64195141137749</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.32332862019327</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.99500740379901</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.07787391884749</v>
       </c>
     </row>
   </sheetData>
@@ -3765,22 +3765,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.42591594422439</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.73268604451997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.75615526834425</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.52417047461233</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.25072437381456</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.32525604506147</v>
+        <v>33.9950165661235</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.23119822735638</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.70042527570347</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.31124749321824</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.77815737577944</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.13545763275419</v>
       </c>
     </row>
   </sheetData>
@@ -3839,22 +3839,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.56975145325136</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.03111445479596</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.44591673205318</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.64685899196949</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.07955741742627</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.78897433403333</v>
+        <v>28.87497145333383</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.90102368041948</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.02240536780912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.47504152576273</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.15920180233898</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.04566858504336</v>
       </c>
     </row>
   </sheetData>
@@ -3913,22 +3913,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.97986741226792</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.20486931873804</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.17112471310337</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.32915797654443</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.04413330640406</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.68613492136119</v>
+        <v>30.70189238669239</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.60407365801023</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.15515142929353</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.31835989922641</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.26934389737564</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.89046402125648</v>
       </c>
     </row>
   </sheetData>
@@ -3987,22 +3987,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.07128051184194</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.39657875883125</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.4006115668427</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.96491691224086</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.29981521795142</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.15527438288672</v>
+        <v>31.12747068355202</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.55655267110148</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.54685492041428</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.67037677390707</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.45351740926095</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.51066908412436</v>
       </c>
     </row>
   </sheetData>
@@ -4061,22 +4061,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.23930643483684</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.65632509866278</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.9551391180714</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.69681881619329</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.66687904609342</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.80324137673104</v>
+        <v>30.44190428627967</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.53644474226627</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.8537847737751</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.24313054125177</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.14731331534851</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.65842928527854</v>
       </c>
     </row>
   </sheetData>
@@ -4135,22 +4135,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.74988110596915</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.68616203020679</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.14989766604458</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.23157731561303</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.09724604227637</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.55099776319697</v>
+        <v>31.36995551028348</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.8066257740548</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.22509711790444</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.36132593829639</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.30662556954653</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.91527632477461</v>
       </c>
     </row>
   </sheetData>
@@ -4209,22 +4209,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.17898331471464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.02097396263139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.11370765266729</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.14113824919261</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.57913590386568</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.5298312485386</v>
+        <v>29.52208057293181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.96281299828496</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.3271747751071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.81614308791064</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.64955748586253</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.53103126427255</v>
       </c>
     </row>
   </sheetData>
@@ -4283,22 +4283,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.44715347685145</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.98455452488322</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.85325453933802</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.47416134118005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.63881812333144</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.48816948236042</v>
+        <v>26.76037642194245</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.46685769208112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.20513925199834</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.62181207119654</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.25019175074666</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.89083647410837</v>
       </c>
     </row>
   </sheetData>
@@ -4357,22 +4357,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.27549717059635</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.77570892388032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.06645725401055</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.15378568155499</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.57525898823949</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.73296527924002</v>
+        <v>43.06871074734821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.64986475374604</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.77845155398497</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.30419231772603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.50285228658891</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.55942584476126</v>
       </c>
     </row>
   </sheetData>
@@ -4431,22 +4431,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53.39687613968687</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.37171852771669</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.32458352101849</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.75435745548294</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.43742981997924</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.88135202695362</v>
+        <v>25.88829671083604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.56361927147956</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.14212458897407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.77852409328581</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.41112157398742</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.62105938465275</v>
       </c>
     </row>
   </sheetData>
@@ -4505,22 +4505,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.14048812520388</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.32893757526269</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.85794354864277</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.03337598920036</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.63214602165155</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.98651495480346</v>
+        <v>31.3775270064176</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.59258524725453</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.93629345606036</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.12413055360781</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.65966454515166</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.19986314092785</v>
       </c>
     </row>
   </sheetData>
@@ -4579,22 +4579,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.72431367524586</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.57647344180513</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.23397350965839</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.01915512883551</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.63021040358992</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.7597619414104</v>
+        <v>28.75127276065146</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.56900688642763</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.64840593217664</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.27232196208414</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.8245513163606</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.36982525171148</v>
       </c>
     </row>
   </sheetData>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.82900414647003</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.622530431963</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.58899753163134</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.58485845028112</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.88351925134856</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.80552931233273</v>
+        <v>38.66129341367791</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.79708900142953</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.36445122136082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.4967632243096</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.20381464115396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.71668340376335</v>
       </c>
     </row>
   </sheetData>
@@ -4727,22 +4727,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.71387534264726</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.97438907630966</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.44628919907342</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.68526968641954</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.77591836912688</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.41848256552709</v>
+        <v>36.69029919589984</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.72488122919012</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.07544499185154</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.70546203777968</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.75762087082803</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.89995899739356</v>
       </c>
     </row>
   </sheetData>
@@ -4801,22 +4801,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.47770727184462</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.74159031826764</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.20974073429391</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.52972841483637</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.09778093238149</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.41242990774536</v>
+        <v>31.7350168454844</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.83624566915585</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.28024688935874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.96861637765473</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.6480817901356</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.17119397840342</v>
       </c>
     </row>
   </sheetData>
@@ -4875,22 +4875,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.20215316148937</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.27825232099077</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.31933407387922</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.2049482773947</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.24448965849098</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.76705111918888</v>
+        <v>28.82703127575135</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.24810765650919</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.33950206812433</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.1465224165493</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.81992003305474</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.07406193838241</v>
       </c>
     </row>
   </sheetData>
@@ -4949,22 +4949,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.16941413203365</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.51300923929178</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.08215237067661</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.29654450385576</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.62234068838328</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.38092334598514</v>
+        <v>32.69942599312815</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.56697881185003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.18453057626893</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.05010904606122</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.10224720596623</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.94319870978761</v>
       </c>
     </row>
   </sheetData>
@@ -5023,22 +5023,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.51274832857699</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.34306281167983</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.04005036289793</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.47841280013818</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.23003593253372</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.13668505937484</v>
+        <v>25.9078500101997</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.93133435790643</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.22901550942101</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.08962198711647</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.73371409211148</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.85269658155185</v>
       </c>
     </row>
   </sheetData>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.06959032182454</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.67696076789362</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.5569316529711</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.312977890367</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.9270031968921</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.88205543281572</v>
+        <v>36.6546362117953</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.54259521443576</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.12779262299976</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.95027486637117</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.03124473121575</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.31652744178243</v>
       </c>
     </row>
   </sheetData>
@@ -5171,22 +5171,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.71894833262515</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.36573670020731</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.92385153210741</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.05752303523921</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.15828296974721</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.82852447583118</v>
+        <v>27.82084116102014</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.55630815811345</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.85167123922883</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.9955885214988</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.29729920491335</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.04299626898744</v>
       </c>
     </row>
   </sheetData>
@@ -5245,22 +5245,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.96093921281403</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.51302083050153</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.06629579217394</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.34014545114477</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.30359861779608</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.32254051938408</v>
+        <v>29.24436423723626</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.31883292549949</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.78967779417047</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.28704310335457</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.69680053079477</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.2188246741534</v>
       </c>
     </row>
   </sheetData>
@@ -5319,22 +5319,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.59828442670224</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.49298835910853</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.72163729906497</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.07257458969703</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.68422939849831</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.22765246821801</v>
+        <v>27.75009254905533</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.46794983073437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.71945910550173</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.79017677583764</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.91302892570046</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.92809592875794</v>
       </c>
     </row>
   </sheetData>
@@ -5393,22 +5393,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.30315398340045</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.93008154793137</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.38690799592296</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.39070789551972</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.65843026439554</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.25952278908743</v>
+        <v>26.58881030605184</v>
+      </c>
+      <c r="C2" t="n">
+        <v>60.96612468884798</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.93891636384131</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.90086528068228</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.27205689483442</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.4185062055609</v>
       </c>
     </row>
   </sheetData>
@@ -5467,22 +5467,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.62398848833188</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.11178985260089</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.80571860132515</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.64320478918614</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.13291249807234</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.34401079931588</v>
+        <v>27.06285309848935</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.52913662175278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.3288557925237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.76025262882867</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.2373443531435</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.96965495162594</v>
       </c>
     </row>
   </sheetData>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.92625301854905</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.5689977972327</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.58815890118093</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.72421080305086</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.07720152526523</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.69626940629064</v>
+        <v>31.87805560084485</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.81086411784721</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.94039784817664</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.26208601429046</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.98725148453085</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.3493825371125</v>
       </c>
     </row>
   </sheetData>
@@ -5615,22 +5615,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.05542504772099</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.68889295527698</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.89810119920853</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.36666207696333</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.76247721108496</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.15435253849746</v>
+        <v>33.6776597558127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.45190778413107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.11496326192974</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.92039663581749</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.10758889092617</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.61272729429601</v>
       </c>
     </row>
   </sheetData>
@@ -5689,22 +5689,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.88097417782889</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.40556524099946</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.55856906774132</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.3068455435381</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.54148567770242</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.00556889132084</v>
+        <v>30.70226250366204</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.20370906957159</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.9734256262983</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.32266093723614</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.53273862460713</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.11045673363622</v>
       </c>
     </row>
   </sheetData>
@@ -5763,22 +5763,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.67895774447623</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.26704695456932</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.92883663722941</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.50787210279154</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.37936991931052</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.37933630378115</v>
+        <v>28.58561883490817</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.55256175373761</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.89578052228575</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.95883874757736</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.91494018413471</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.1500207705175</v>
       </c>
     </row>
   </sheetData>
@@ -5837,22 +5837,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.14383093327653</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.77517339671088</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.68182418902679</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.21656454735492</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.68986936318945</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.9589083635383</v>
+        <v>32.95601054933652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.0535828055223</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.13821376754981</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.29329386351202</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.56595720987325</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.33078064253424</v>
       </c>
     </row>
   </sheetData>
@@ -5911,22 +5911,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.58866671982771</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.06109383792177</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.80104351228582</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.04223407943314</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.2368539300671</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.47312708317442</v>
+        <v>26.3684151982037</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.82009018664599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.21078045264006</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.35085554541194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.35132737192396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.38834595258377</v>
       </c>
     </row>
   </sheetData>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.90486367162997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.77636267665572</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.34997155744448</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.94822862166197</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.00005378019157</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.56219575486458</v>
+        <v>35.19549620832146</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.93525351029028</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.18316390345395</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.137913333378</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.99402469391114</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.08787351232509</v>
       </c>
     </row>
   </sheetData>
@@ -6059,22 +6059,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.48025651196969</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.96097894335811</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.26298070179815</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.22638291681147</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.21314235057282</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.17777094441487</v>
+        <v>32.2888204837658</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.36693211050375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.60428122582115</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.06035843907458</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.54559971657217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.28051791072468</v>
       </c>
     </row>
   </sheetData>
@@ -6133,22 +6133,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.61603447102637</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.14333257966648</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.32305998097007</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.04431344407392</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.12206862879484</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.28834881626557</v>
+        <v>27.65458863735388</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.83399552291993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.39446138757954</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.28442384863127</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.72138244226224</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.02443624955173</v>
       </c>
     </row>
   </sheetData>
@@ -6207,22 +6207,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.03807524364277</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.75667641805118</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.12856163091757</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.64650667194376</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.00827831982894</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.37531918671925</v>
+        <v>34.30953334565511</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.57465680771521</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.73883293236329</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.11662164603943</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.5626784286003</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.14212755794852</v>
       </c>
     </row>
   </sheetData>
@@ -6281,22 +6281,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.13232036447792</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.73831988899561</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.55020864555972</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.91584146190028</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.2092052421745</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.48834751447698</v>
+        <v>38.13505768002114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.83752633574184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.12372493118646</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.44983848082678</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.36716288982878</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.53559215682524</v>
       </c>
     </row>
   </sheetData>
@@ -6355,22 +6355,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.83183077527793</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.47110766104045</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.20757598597583</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.66214343138448</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.75273312425391</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.27946318352272</v>
+        <v>26.05228127044525</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.4184635627869</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.60357006479217</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.12692307105305</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.10311845397058</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.64618970903965</v>
       </c>
     </row>
   </sheetData>
@@ -6429,22 +6429,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.48326096558979</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.98790439410931</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.68694977306961</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17.36155415453204</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.59475590964099</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.67937177997634</v>
+        <v>27.61225563439685</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.14142629732084</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.58367900457942</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.2425478278526</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.8935084836741</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.76923073637813</v>
       </c>
     </row>
   </sheetData>
@@ -6503,22 +6503,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.34982379296172</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.97569898091503</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.71647564948164</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.94377255548982</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.82623260035274</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.13280675617938</v>
+        <v>27.61399168224047</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.44499498857788</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.0696703501206</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.75784311114189</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.86835766712531</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.58882262433173</v>
       </c>
     </row>
   </sheetData>
@@ -6577,22 +6577,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.67156318588252</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.56052018777464</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.50338712822655</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.07779028291995</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.68555474277817</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.63771871869382</v>
+        <v>33.0287294582587</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.37613959960736</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.88150341117979</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.87396178976702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.0113266398624</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.98046645051663</v>
       </c>
     </row>
   </sheetData>
@@ -6651,22 +6651,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.93122703672412</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.60081590561609</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.88029769955938</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.40016238239986</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.87397511805111</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.02271917346528</v>
+        <v>29.84205619724896</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.87067396901422</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.48944383545289</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.39481945732776</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.84346921235142</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.9389077263648</v>
       </c>
     </row>
   </sheetData>
@@ -6725,22 +6725,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.39337193630442</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.70525524735564</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.04836058180651</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.79459033650038</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.49558611134416</v>
-      </c>
-      <c r="G2" t="n">
-        <v>50.14556826066254</v>
+        <v>36.71249803126254</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.97084733736144</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.32897508565409</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.93830511967634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.41731638069907</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.82137415188501</v>
       </c>
     </row>
   </sheetData>
@@ -6799,22 +6799,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.84643332190469</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.49853922370039</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.50607310494912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>54.59963058703238</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.69003124175927</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.00983036419684</v>
+        <v>32.23159607130088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.92257375415139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.72347084183833</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.88639382505371</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.74982434256512</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.28183654379566</v>
       </c>
     </row>
   </sheetData>
@@ -6873,22 +6873,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.83798009388221</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.47604270769854</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.69171390708281</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.61256140806132</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.20905557134927</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.4036352309862</v>
+        <v>31.32671809111525</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.02194703795843</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.54724469813901</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.74669368714049</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.22208824703811</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.57947525801761</v>
       </c>
     </row>
   </sheetData>
@@ -6947,22 +6947,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.89765675870268</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.63130978722372</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.72933588305215</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.04521406201872</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.04271955248804</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.94178221059643</v>
+        <v>31.10465992980312</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.86769558563572</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.84383334983725</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.97167098156189</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.3634921983456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.74427417818862</v>
       </c>
     </row>
   </sheetData>
@@ -7021,22 +7021,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.82779944726898</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.48884452369673</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.85429152215064</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.6579273370536</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.22803662590169</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.37798612703406</v>
+        <v>30.94106987649134</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.28042675034543</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.72236076543273</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.46468563048041</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.52958093406045</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.00325065129087</v>
       </c>
     </row>
   </sheetData>
@@ -7095,22 +7095,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.85198994581647</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.61089605382497</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.09719210295275</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.25496596940166</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.73024786670196</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.63427791135678</v>
+        <v>25.27617002625037</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.55932780049999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.3927880279053</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.34325471999104</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.37018905803432</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.43100170616452</v>
       </c>
     </row>
   </sheetData>
@@ -7169,22 +7169,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.56882820475559</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.8164870787883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.62856997661993</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.28235198552197</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.58471368429016</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.7682849170208</v>
+        <v>29.74341466091793</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.02125943585916</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.13412114326538</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.89615705864523</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.87667608643974</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.56961387578334</v>
       </c>
     </row>
   </sheetData>
@@ -7243,22 +7243,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.66617507115124</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.39770801581918</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.33111539303603</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.93222173653922</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.07902158409628</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.49225389473711</v>
+        <v>24.71678127628696</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.15900611283443</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.73702715644274</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.51105552268661</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.28998308308463</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.1761599578434</v>
       </c>
     </row>
   </sheetData>
@@ -7317,22 +7317,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.54990934371401</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.44264280452528</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.06744759907496</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.7065988529152</v>
-      </c>
-      <c r="F2" t="n">
-        <v>52.90246481863711</v>
-      </c>
-      <c r="G2" t="n">
-        <v>51.81570178336985</v>
+        <v>30.95005102170622</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.20231140381743</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.34917129238445</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.77772994023428</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.04259505704916</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.96775010167092</v>
       </c>
     </row>
   </sheetData>
@@ -7391,22 +7391,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.17174060449274</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.17645463293056</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.43286085142284</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.92854018537085</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.40092109900256</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.28484739937173</v>
+        <v>33.40830788816728</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.61501288413133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.41065526649383</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.06988381939727</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.80177397680288</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.62949687681211</v>
       </c>
     </row>
   </sheetData>
@@ -7465,22 +7465,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.81840488049187</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.27701082738793</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.18386632514324</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.21650562842979</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.84023871007416</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.61707235682668</v>
+        <v>23.92002239542994</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.98187147026636</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.35085778566376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.08656685836132</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.5966212493568</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.87876085433992</v>
       </c>
     </row>
   </sheetData>
@@ -7539,22 +7539,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.12809865225756</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.75403343565701</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.40018120274082</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.22750504134697</v>
-      </c>
-      <c r="F2" t="n">
-        <v>48.64859763435335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.0511729270107</v>
+        <v>26.22240889432835</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.96262462018982</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.82535530241649</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.70453703311572</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.06529104614157</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.19489789491233</v>
       </c>
     </row>
   </sheetData>
@@ -7613,22 +7613,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.99813644543372</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.37113260690914</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.47856150118287</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.61732814837728</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.08691073529047</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.1780969850033</v>
+        <v>27.15402661143965</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.29851863934461</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.06877190305442</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.59536920640757</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.01382455571805</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.80995017322897</v>
       </c>
     </row>
   </sheetData>
@@ -7687,22 +7687,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.8993574725589</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.99190051335395</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.26716514803477</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.93829173634514</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.40333181582551</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.08987021496533</v>
+        <v>30.54750666222281</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.9524954055486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.77149652728625</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.79825287515259</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.45680002312673</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.05156753611958</v>
       </c>
     </row>
   </sheetData>
@@ -7761,22 +7761,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.00910594124147</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.74528308013984</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.47556236921201</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.77000820469122</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12.51455458658842</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.4434126599314</v>
+        <v>31.66129508557383</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.78498103511765</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.29484450507246</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.45550939556398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.05267113651866</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.92527419335462</v>
       </c>
     </row>
   </sheetData>
@@ -7835,22 +7835,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.0541111421741</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.49372078104167</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.53474821377122</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.83730920990187</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.03374588368483</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.14992493369152</v>
+        <v>43.45971409914834</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.49304169594039</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.13796823817407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.8021225660332</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.45711477864217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.70985378714744</v>
       </c>
     </row>
   </sheetData>
@@ -7909,22 +7909,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.60132767120521</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.38897286023928</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.39376096777076</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.28008687373951</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.05335605744323</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.40982014496991</v>
+        <v>36.80875115204626</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.07744410935389</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.72888274357857</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.75876988620166</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.53050336629122</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.51278039467532</v>
       </c>
     </row>
   </sheetData>
@@ -7983,22 +7983,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.98963854460852</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.19872869488027</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.07511727762213</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.67826726604253</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.63490952341177</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.12774994171846</v>
+        <v>29.73302177763177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.3793082731595</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.65142424889407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.0475553490123</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.71802371189844</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.27982476785482</v>
       </c>
     </row>
   </sheetData>
@@ -8057,22 +8057,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.62915912360484</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.13571737363137</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.63245608376783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.18544614242722</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.36742113274531</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.06348304549714</v>
+        <v>27.16483643655506</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.32122974864336</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.90330034853795</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.8104250591256</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.2721789255707</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.80977235501767</v>
       </c>
     </row>
   </sheetData>
@@ -8131,22 +8131,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.97217343042305</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.76211164887986</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.85109940850917</v>
-      </c>
-      <c r="E2" t="n">
-        <v>51.16359801829774</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.24905969062343</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.80976469834739</v>
+        <v>34.91029366698994</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.88379243110005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.27809423950048</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.53768050733477</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.92042392036219</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.69328471962812</v>
       </c>
     </row>
   </sheetData>
@@ -8205,22 +8205,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.31930994480736</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50.43459799812592</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.18641581281848</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.70183403736032</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.0975397496848</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.99632020492353</v>
+        <v>27.01435502668637</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.91687942820437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.39467248274232</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.32392563617769</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.15126119253897</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.2298298791867</v>
       </c>
     </row>
   </sheetData>
@@ -8279,22 +8279,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.04986942859441</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.03526438091389</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.9061621595306</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.85831969703175</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.06251342431408</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.95539924850837</v>
+        <v>30.55461592708128</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.6276406258221</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.65726911217319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.72855878173577</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.68434629157855</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.18536231854364</v>
       </c>
     </row>
   </sheetData>
@@ -8353,22 +8353,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.95036045673534</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.53939403094512</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.85690614835258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.02438371262632</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.94059204513741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.68852407574946</v>
+        <v>27.37886869189861</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.48022592959826</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.87363922067187</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.69158711805566</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.03575475276507</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.94212259770629</v>
       </c>
     </row>
   </sheetData>
@@ -8427,22 +8427,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.08127709211089</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.84964628247224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.07378617720695</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.66472497091048</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.01778314967936</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.16106221893313</v>
+        <v>30.18629092058805</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.58400272405097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.22743048658116</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.57554232795798</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.46421924428737</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.89521867092992</v>
       </c>
     </row>
   </sheetData>
@@ -8501,22 +8501,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.63223592619594</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.58466383554719</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.41312452362571</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.14579512395185</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.28528136101076</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.27379295099053</v>
+        <v>41.3503866907578</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.13368784908171</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.75299367284067</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.36362511717938</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.78126895519745</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.62908734334692</v>
       </c>
     </row>
   </sheetData>
@@ -8575,22 +8575,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.18216456775271</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.89576249640334</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.85650352182754</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.19086546548959</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.26322504943652</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.64055909070718</v>
+        <v>33.67788630697969</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.283834914862</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.61547065035624</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.03812011582029</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.98782811175833</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.39201782179338</v>
       </c>
     </row>
   </sheetData>
@@ -8649,22 +8649,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.88481561943264</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.09354105652461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.27862413470752</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.67211278257685</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.02162076059016</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.09123731409476</v>
+        <v>29.25385531722047</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.80094071441273</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.57581608130449</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.04944340504694</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.49691966415623</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.52486467812038</v>
       </c>
     </row>
   </sheetData>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.36261489726092</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.23990907105233</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.04187175340247</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.34719690967509</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.9845748901794</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.91369176964066</v>
+        <v>26.48478938752297</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.01189607146061</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.75678920288912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.30588104348844</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.17869294370604</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.55539287795549</v>
       </c>
     </row>
   </sheetData>
@@ -8797,22 +8797,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.04967898297601</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.50716010919039</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.81635064824316</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.69521066208102</v>
-      </c>
-      <c r="F2" t="n">
-        <v>53.78590229243562</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.04140330823073</v>
+        <v>31.17073113178593</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.42590893250107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.70536156763242</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.0601229181724</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.79831673782899</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.62122068923618</v>
       </c>
     </row>
   </sheetData>
@@ -8871,22 +8871,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.64920492069607</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.26041183145677</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.31600748722795</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.27920188518759</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.39635554963131</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.04306400293351</v>
+        <v>31.56360119439712</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.6151123100737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.56710547933547</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.64636091696228</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.29939147893424</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.95506137092799</v>
       </c>
     </row>
   </sheetData>
@@ -8945,22 +8945,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.78744655998701</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.30763913329521</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.03313784581064</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.4298840858613</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.99105947140401</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.54559299412065</v>
+        <v>34.47658474652372</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.3633424705687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.80998218676114</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.46267995422973</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.7281693017656</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.70525892544394</v>
       </c>
     </row>
   </sheetData>
@@ -9019,22 +9019,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.6671222754904</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.36964390441711</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.88571034171978</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.0364190062607</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.60865519252346</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.07221271732855</v>
+        <v>27.75685615541501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.69240833116289</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.13495414375203</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.691255133603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.38719628492945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.40999178408636</v>
       </c>
     </row>
   </sheetData>
@@ -9093,22 +9093,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.02989033941501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.30720281471896</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.12013702305602</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.27584346571449</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.73376236848631</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.65391407231375</v>
+        <v>26.22004781451245</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.99465859620761</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.6566195380761</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.42936115717433</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.12068796555299</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.46131101940848</v>
       </c>
     </row>
   </sheetData>
@@ -9167,22 +9167,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.16072740815581</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.99905191211185</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.96391239234998</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.6614557288997</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.4184414984209</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.08786651340133</v>
+        <v>27.38444954257583</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.87019860018642</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.40967994677487</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.03468883913095</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.20163822672789</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.5665348987508</v>
       </c>
     </row>
   </sheetData>
@@ -9241,22 +9241,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.62731340402684</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.39903818600656</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.6430344793053</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.38113780646118</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.20933563466257</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.26655176320462</v>
+        <v>29.63390930773118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.42145255369747</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.01676739348685</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.26067845047145</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.60364171080634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.4781754894616</v>
       </c>
     </row>
   </sheetData>
@@ -9315,22 +9315,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.63128812663652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.79027729650655</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.53185069112387</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.57029570105374</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.47544408094073</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.55739058030561</v>
+        <v>29.12553106790132</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.92783096305564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.79980105306755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.98112241620984</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.91967166475651</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.47941178382824</v>
       </c>
     </row>
   </sheetData>
@@ -9389,22 +9389,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.70131481756826</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.84591700235634</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.71154085884871</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.09134354037465</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.09625460184617</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.46887353103396</v>
+        <v>29.03011178904736</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.95263530210396</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.80942996400712</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.7569774814434</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.25260568213535</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.15076905311432</v>
       </c>
     </row>
   </sheetData>
@@ -9463,22 +9463,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.34387311651812</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.88773501778966</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.80276053672344</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.61089505376635</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.02243204470828</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.61112656877115</v>
+        <v>31.88309891629861</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.57225741377907</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.28318793766984</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.10858115522598</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.81705903766662</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.82271185849104</v>
       </c>
     </row>
   </sheetData>
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.24662689032637</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.72202932103084</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.52360418776697</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.49631197084262</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.28086489206876</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.50945100276739</v>
+        <v>35.55297442578177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.18681190590996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.93934236098944</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.92809471211131</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.94920051821035</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.25870003614282</v>
       </c>
     </row>
   </sheetData>
@@ -9611,22 +9611,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.67684832428563</v>
-      </c>
-      <c r="C2" t="n">
-        <v>705.9943318019316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.58261845167833</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.4671891480691</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.78401671117903</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.05306851684919</v>
+        <v>29.76787299819279</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.81607471992286</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.77509819006398</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.63489817207474</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.69234360196975</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.61536112368932</v>
       </c>
     </row>
   </sheetData>
@@ -9685,22 +9685,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.40710790947733</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.15868107972793</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.09625486816507</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.20146370931418</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.24846098677254</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.00856936204661</v>
+        <v>26.61881719296352</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.59594163621239</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.38505103261613</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.51684687416838</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.80697484677444</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.04002759565522</v>
       </c>
     </row>
   </sheetData>
@@ -9759,22 +9759,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.23057773254287</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.60653298468036</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.71704145211781</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.39319594614225</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.31181320840258</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.10566448436649</v>
+        <v>27.70888684408261</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.49048653095235</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.27131635066529</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.2911360649038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.41190286443161</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.21192138631524</v>
       </c>
     </row>
   </sheetData>
@@ -9833,22 +9833,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.93101436633177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.3017999999687</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.99970129818878</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.08480915952968</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.24579555603496</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.62087353108679</v>
+        <v>28.65448203243242</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.65942265544044</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.06759720285408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.3602852820619</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.91146149093891</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.78043469670365</v>
       </c>
     </row>
   </sheetData>
@@ -9907,22 +9907,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.23131296697702</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.45664216528625</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.96438739633197</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.40630992003628</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.96329889596598</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.59549249482239</v>
+        <v>31.3003012689092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.15974067987602</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.86570101011176</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.92959858132426</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.28674630909524</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.97152340827686</v>
       </c>
     </row>
   </sheetData>
@@ -9981,22 +9981,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.71812577729697</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.85531288832069</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.12174652164207</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50.8753305920367</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.13673719593884</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.9626213539614</v>
+        <v>26.19714537733299</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.75050654795047</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.47828382306027</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.42135488719137</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.92520978093983</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.60947169162606</v>
       </c>
     </row>
   </sheetData>
@@ -10055,22 +10055,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.98517752700371</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.93884613815123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.15532952160778</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.78949010790583</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.34706939302652</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.51951940516279</v>
+        <v>28.45398939053131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.56174100334315</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.74057631666302</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.73601705976193</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.78204528140067</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.76052696124771</v>
       </c>
     </row>
   </sheetData>
@@ -10129,22 +10129,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.17191934400134</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.64227311977026</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.21363128052888</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.33033543669173</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.79108072390753</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.83398932291096</v>
+        <v>27.48222467468864</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.60795469567884</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.55126559919078</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.21740210570003</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.7741549193904</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.22509862732166</v>
       </c>
     </row>
   </sheetData>
@@ -10203,22 +10203,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.84928702952501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>64.83917706904489</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.73275196665397</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.61692924386912</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.15250065836361</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.17601702109323</v>
+        <v>29.05882183258849</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.45184182273097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.76115848880882</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.1515188953756</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.05696138903537</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.27967665504157</v>
       </c>
     </row>
   </sheetData>
@@ -10277,22 +10277,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.28546165629573</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.41995957374593</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.40016255533261</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.01511973382456</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.13436296410624</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.98916649073134</v>
+        <v>21.8522260664173</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.48963265485632</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.62523166927532</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.66272972789586</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.8338082118882</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.15697171291927</v>
       </c>
     </row>
   </sheetData>
@@ -10351,22 +10351,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.30639463503132</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.62997294567094</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.06624294451326</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.83363579370107</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.25059943172198</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.36639454891267</v>
+        <v>34.92829471149156</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.4697643880662</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.58558432612998</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.9356833554333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.28838544464849</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.18622288936268</v>
       </c>
     </row>
   </sheetData>
@@ -10425,22 +10425,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.28507504544253</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.76391723821534</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.12199691901388</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.2926887988544</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.75120871111555</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.94003149349236</v>
+        <v>29.23865109024154</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.24485157226231</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.63973569885494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.43870663619531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.78710075707824</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.20621224537463</v>
       </c>
     </row>
   </sheetData>
@@ -10499,22 +10499,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.34765194948103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.61978806814921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.59090840786626</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.84120146032875</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.21166118502408</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.24757544758789</v>
+        <v>36.19756584380114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.20459861335648</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.46482943666668</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.42618877887549</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.86051575729958</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.76463672059486</v>
       </c>
     </row>
   </sheetData>
@@ -10573,22 +10573,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.81904212751302</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.55710345091171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.14982071027023</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.73345034177026</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.58631111550914</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.49717082160937</v>
+        <v>32.59662836814764</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.20662713805999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.27487557358914</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.80035940178476</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.52867762064842</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.54290236712551</v>
       </c>
     </row>
   </sheetData>
@@ -10647,22 +10647,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.8513296439181</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.33698902010491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.83723856549843</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.13787109418815</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.03151709396894</v>
-      </c>
-      <c r="G2" t="n">
-        <v>54.87666463902502</v>
+        <v>28.55501379230969</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.78499342015055</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.18918048513198</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.94681632094214</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.33418690967584</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.27522616450224</v>
       </c>
     </row>
   </sheetData>
@@ -10721,22 +10721,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.72446861397059</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.95838849947674</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.39900673782781</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.47070594178937</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.12005068426193</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.246528765355</v>
+        <v>30.50333316237576</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.01668763950244</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.06551118675879</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.13877320607859</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.34881494333708</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.78739353041604</v>
       </c>
     </row>
   </sheetData>
@@ -10795,22 +10795,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.27565782561916</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.43032925228538</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.3416674208129</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.32682661442519</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.16329270490257</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.81737877505788</v>
+        <v>30.42844688069902</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.23141300246485</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.39576486151128</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.26860865239444</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.34943047204212</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.13952064175763</v>
       </c>
     </row>
   </sheetData>
@@ -10869,22 +10869,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.18802449140547</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.71317737681299</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.65480151246791</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.71773492979329</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.6057851205016</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.82963133695975</v>
+        <v>19.97113402945381</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.28390596391339</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.50914834903573</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.78417141882961</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.28262914539023</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.88932434364594</v>
       </c>
     </row>
   </sheetData>
@@ -10943,22 +10943,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.35019362385333</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.03141860522615</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.6982379185783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.86266251392972</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.73262649738648</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.16934439991893</v>
+        <v>44.3478875328512</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.81633479683251</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.22538853539677</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.90767751053912</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.4490245450058</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.60889804924123</v>
       </c>
     </row>
   </sheetData>
@@ -11017,22 +11017,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.38168411768242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50.78283880242292</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15.47317251450625</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.07506625364737</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.32706081171371</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.72311889638551</v>
+        <v>32.06662444455056</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.00975095745195</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.58270837771244</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.82988948998474</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.90444015403808</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.36716190103634</v>
       </c>
     </row>
   </sheetData>
@@ -11091,22 +11091,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.20264360140373</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.73182909757492</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.72723408767242</v>
-      </c>
-      <c r="E2" t="n">
-        <v>53.66633853986483</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.83671100977595</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.30406670705455</v>
+        <v>33.66065340698557</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.23716870324612</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.73062400002742</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.49415578304993</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.3007760400186</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.36223758616517</v>
       </c>
     </row>
   </sheetData>
@@ -11165,22 +11165,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.38561703402581</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.56041953285296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.89866856640124</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.88681124118082</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.79525528603244</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.39486160006152</v>
+        <v>27.49717677491792</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.6620143103576</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.21284879438173</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.47502195889327</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.86674789557705</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.47456517245718</v>
       </c>
     </row>
   </sheetData>
@@ -11239,22 +11239,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.1689781345891</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.78661572617489</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.68097171635137</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.1560849722725</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.82290278631834</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.20110646351225</v>
+        <v>32.05382526789582</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.96985904044401</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.75213273318321</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.71343689228179</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.40299570167766</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.15525981775339</v>
       </c>
     </row>
   </sheetData>
@@ -11313,22 +11313,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.86485531134236</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.38737186888993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.23972171030417</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.63071988744501</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.90592946269589</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.21126028895325</v>
+        <v>29.59882522528177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.9146568568034</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.08853568023824</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.94232348151027</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.16853936564893</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.03982023337876</v>
       </c>
     </row>
   </sheetData>
@@ -11387,22 +11387,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.41267530837032</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.89722906975052</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.51069110187449</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.61475479395963</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.57439545972056</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.56115203466398</v>
+        <v>32.9570945144574</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.2318265622486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.88269512408285</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.60676502841622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.82602034915766</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.30132044711622</v>
       </c>
     </row>
   </sheetData>
@@ -11461,22 +11461,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.29441880734188</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.10723872405038</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.85509995463686</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.68894001301605</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.04252080951785</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.68101924386369</v>
+        <v>25.16058993840176</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.1798959991355</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.20940382370008</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.04866801042092</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.9030522718806</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.16946978521319</v>
       </c>
     </row>
   </sheetData>
@@ -11535,22 +11535,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.35284076425955</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.73654743506197</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.92828504183616</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.99207525378626</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.07725169281283</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.81650156548695</v>
+        <v>44.71597020393326</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.35870422387602</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.42089619759209</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.27881363589003</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.2035384118789</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.50663828066313</v>
       </c>
     </row>
   </sheetData>
@@ -11609,22 +11609,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.722556227212</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.87051831305356</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.19972892990989</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.81956765653759</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.70580834772215</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.96571308567386</v>
+        <v>40.03290998981296</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.27694677168563</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.62824313315529</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.83024437867297</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.67559179403939</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.26046881874042</v>
       </c>
     </row>
   </sheetData>
@@ -11683,22 +11683,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.10661450320389</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.62820876076921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.53897839189523</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.69629391125454</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.54856249413973</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.28805025186162</v>
+        <v>34.02992571139968</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.75204572917282</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.61982438703928</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.81513788004249</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.07689461601659</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.66217492909659</v>
       </c>
     </row>
   </sheetData>
@@ -11757,22 +11757,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.16035397053707</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.70472439041847</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.05602649245897</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.53541976777276</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.40903458272799</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.79391349015523</v>
+        <v>27.9139293919518</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.65984602569243</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.43606922839884</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.05192970019559</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.63441043783379</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.1216120739311</v>
       </c>
     </row>
   </sheetData>
@@ -11831,22 +11831,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.92974279784491</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.41336948206526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.64874333057885</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.26380997820059</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.8088047070913</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.70029483541495</v>
+        <v>26.26117953037295</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.44148134011236</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.35282307004408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.05846227695876</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.09444984775645</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.56504855531232</v>
       </c>
     </row>
   </sheetData>
@@ -11905,22 +11905,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.56717977887235</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.04497301559479</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.41069825527225</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.42038005250778</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.82445612004511</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.26588313934077</v>
+        <v>34.81128752079946</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.06171118757766</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.10723404319344</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.19518490388136</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.40972871258656</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.03192845970149</v>
       </c>
     </row>
   </sheetData>
@@ -11979,22 +11979,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.79533808354179</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.24967047121132</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.63241718253939</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.40964495614461</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.24105324118071</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.67707949025289</v>
+        <v>34.61985784844012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.72944567625364</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.45093222318509</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.42867928848124</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.26929438238388</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.29709842533919</v>
       </c>
     </row>
   </sheetData>
@@ -12053,22 +12053,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.9481882105577</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.55493390381865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.42112719879037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.30529316661586</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.06998837956128</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.84575290111808</v>
+        <v>29.82984518698572</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.62343658779861</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.24875947047252</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.09375466595917</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.95928124507881</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.21479572723725</v>
       </c>
     </row>
   </sheetData>
@@ -12127,22 +12127,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.17712686454994</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.27320198981663</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.94970275036505</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.31387853815418</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.33618179127336</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.79365906100348</v>
+        <v>32.57212765652781</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.02327500697324</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.82010701955146</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.47654365862251</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.27653077133343</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.89259250351461</v>
       </c>
     </row>
   </sheetData>
@@ -12201,22 +12201,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.8905722508635</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.66770263824328</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.65784643460317</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.85067370585584</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.61684572391239</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.93936929939764</v>
+        <v>26.60525616759508</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.84960504502772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.69743420802537</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.27854019647736</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.27727246006335</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.50524496904913</v>
       </c>
     </row>
   </sheetData>
@@ -12275,22 +12275,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.32959396750731</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.81520011631779</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.80407828873801</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.451724921212</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.15003937901883</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.90772612298748</v>
+        <v>23.10967747524654</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.62138153096877</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.00757284981335</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.44599164015972</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.43395739573358</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.55060245478789</v>
       </c>
     </row>
   </sheetData>
@@ -12349,22 +12349,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.53718385728572</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.17723215144101</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.6140451167567</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.862988180579</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.88477781927191</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.34257487749047</v>
+        <v>31.30098901666373</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.87140075767529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.72650909359426</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.22112605539976</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.81076019499452</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.22567741245846</v>
       </c>
     </row>
   </sheetData>
@@ -12423,22 +12423,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.32646474260459</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.27450673487109</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.52170407408566</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.99960547675748</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.75614663774166</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.20351243789318</v>
+        <v>35.71649768880367</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.05889988678796</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.03892107548378</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.47371831235974</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.64146425181982</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.06130805074894</v>
       </c>
     </row>
   </sheetData>
@@ -12497,22 +12497,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.69553506157287</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.48118548687291</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.73167544420144</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.00652131733629</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.17902078013781</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.14638396842444</v>
+        <v>29.0970075662066</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.05598747650173</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.35481808686839</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.78826046759492</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.93926566073196</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.74424090632055</v>
       </c>
     </row>
   </sheetData>
@@ -12571,22 +12571,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>13.03438198166626</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.45394708631023</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.23979089231199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>56.08942626300569</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.23744449741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.64437223713918</v>
+        <v>25.13422778970746</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.41690668761825</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.53976067112328</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.91870234031424</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.91021371835173</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.78050679666688</v>
       </c>
     </row>
   </sheetData>
@@ -12645,22 +12645,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.80813416393462</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.97614032840925</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.13496813004028</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.00893856900215</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.18855381831937</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.64605476966397</v>
+        <v>27.01099503285853</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.88390854382852</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.26658284590045</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.20752350422527</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.90311685517932</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.41378392354125</v>
       </c>
     </row>
   </sheetData>
@@ -12719,22 +12719,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.39089620871937</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.15279126673095</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.31331689589121</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.1789352250055</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.6660589926478</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.6134601010493</v>
+        <v>32.35842954642631</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.5095513391906</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.69981719035651</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.94300539847909</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.37985871266502</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.16209680724803</v>
       </c>
     </row>
   </sheetData>
@@ -12793,22 +12793,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.96369283945677</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.68385983043989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.28633779346211</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.64771921063294</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.23035420519656</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.16221338287652</v>
+        <v>27.55373682192764</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.255376744054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.30074288333709</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.57886424319553</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.29065907158419</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.2731717075064</v>
       </c>
     </row>
   </sheetData>
@@ -12867,22 +12867,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.18150691882537</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.80455469248109</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.79719163471255</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.66910585729637</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.83572380369048</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.28386494966432</v>
+        <v>36.14060194129406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.03483820478828</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.0929387571197</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.89484454640306</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.24748529326973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.23441967192154</v>
       </c>
     </row>
   </sheetData>
@@ -12941,22 +12941,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.44539972740301</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.07706475609299</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.12070909283479</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.95147091426928</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.98419309144528</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.73061144567063</v>
+        <v>33.71770504541749</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.16333650195171</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.12086710451776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.53511465605893</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.96564560400911</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.82848486740529</v>
       </c>
     </row>
   </sheetData>
@@ -13015,22 +13015,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.21582480532295</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.18249403078976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.03202882545715</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.26610807612256</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.48705331450316</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.60490782919071</v>
+        <v>26.17274704545174</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.42049291557644</v>
+      </c>
+      <c r="D2" t="n">
+        <v>56.03611122519111</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.93734685263603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.66688439478448</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.09308024662533</v>
       </c>
     </row>
   </sheetData>
@@ -13089,22 +13089,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.00975198320689</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.47857993039927</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.92889872848395</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.29631971097599</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.444212594033</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.33871672348307</v>
+        <v>27.0566245650536</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.35778926668433</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.23347480783849</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.61862272640489</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.47213288668302</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.54979230676096</v>
       </c>
     </row>
   </sheetData>
@@ -13163,22 +13163,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.80181357872457</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.1373411227522</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.5738967654138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.50699682632482</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.69052383302828</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.51855037084536</v>
+        <v>26.52634671767028</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.95646727635999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.97393450809597</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.75622212879648</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.17595997158869</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.4457065606034</v>
       </c>
     </row>
   </sheetData>
@@ -13237,22 +13237,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.32779435506109</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.70519333837343</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.16429998453209</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.92261794131096</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.9670940209482</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.66342673003748</v>
+        <v>42.21329689265695</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.69005595934311</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.94341106044821</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.18051836550362</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.84791278313011</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.2616292948972</v>
       </c>
     </row>
   </sheetData>
@@ -13311,22 +13311,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.67243070708871</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.49550282046101</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.6236634830145</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.76197778715834</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.13877874964392</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.59317553236518</v>
+        <v>29.99148898450356</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.61150853697844</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.76230346214115</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.79413459153526</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.81790790177153</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.3962298465638</v>
       </c>
     </row>
   </sheetData>
@@ -13385,22 +13385,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.11210222092033</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.66158118240286</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.89706365296474</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.19558482361693</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.50837295284495</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.70312994372944</v>
+        <v>36.04134997495652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.49388412579829</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.44027244859033</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.56109444221283</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.0186130924811</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.0510435118772</v>
       </c>
     </row>
   </sheetData>
@@ -13459,22 +13459,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.50485395901697</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.96125346994647</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.51923836522128</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.74269140577566</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.08384189553509</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.50004145520117</v>
+        <v>34.85588732346753</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.23929364666033</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.22919621268719</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.82230923958443</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.31354478840924</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.92002694467894</v>
       </c>
     </row>
   </sheetData>
@@ -13533,22 +13533,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.00116045101312</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.83501129395444</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.17699544696516</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.40951546898525</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.78150762071627</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.22507063808534</v>
+        <v>34.32694075929734</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.62286017182845</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.88070125255734</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.17749693460592</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.69172607593577</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.99178319344279</v>
       </c>
     </row>
   </sheetData>
@@ -13607,22 +13607,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.97627660817992</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.70369680011591</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.2473880549008</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.47291526639238</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.66481498071789</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.10118337850606</v>
+        <v>31.7838619523486</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.64942522373008</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.42941154051761</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.95627127591154</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.57310961225217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.0100587830335</v>
       </c>
     </row>
   </sheetData>
@@ -13681,22 +13681,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.55882294413755</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.93569470920686</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.35247316482486</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.15926106783671</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.77943827225143</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.50727780429178</v>
+        <v>29.72829860514662</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.02993601239107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.75884466227637</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.58993676545353</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.53959905283056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.92180633597417</v>
       </c>
     </row>
   </sheetData>
@@ -13755,22 +13755,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.50459837608568</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.87481624254371</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.61318019620954</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.51098801066478</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.05902685209851</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.63049283342353</v>
+        <v>28.58069026626948</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.85919782634582</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.19831867861593</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.01748881076946</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.8466333943819</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.33319420163704</v>
       </c>
     </row>
   </sheetData>
@@ -13829,22 +13829,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.81226551156623</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.70179539687798</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.51635132915574</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.36961185497667</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.92968762128125</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.14344968518619</v>
+        <v>25.80362038537186</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.76099058520791</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.21390543557236</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.00706382750381</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.81895305213356</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.20501422801143</v>
       </c>
     </row>
   </sheetData>
@@ -13903,22 +13903,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.64051027940044</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.77546701727069</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.26801997055362</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.31157142212487</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.9804036745084</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.12491247708255</v>
+        <v>32.62362506385556</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.09229522351441</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.95763795700824</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.30592904535539</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.97885764336108</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.43483410988102</v>
       </c>
     </row>
   </sheetData>
@@ -13977,22 +13977,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.14331859976119</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.9114827176417</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.65219365159016</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.43989850468499</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.39156646387906</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.82173984497455</v>
+        <v>30.62549088269482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.4406974203449</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.34057719495185</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.57381010527217</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.05516425198065</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.45493106024122</v>
       </c>
     </row>
   </sheetData>
@@ -14051,22 +14051,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.25363641886334</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.07024599210546</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.87181567042494</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.06827041278558</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.84593022484334</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.61693037290444</v>
+        <v>28.58567759210592</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.66857815441044</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.34771667664893</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.5845378243153</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.01178809038377</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.59128577818097</v>
       </c>
     </row>
   </sheetData>
@@ -14125,22 +14125,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.21969836130112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.08029751777117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.75115826144408</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.17513333025931</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.69024177681384</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.12286713692055</v>
+        <v>26.33297547222325</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.6216917272872</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50.64065331977852</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.01616160768117</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.17388880075978</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.54094115987603</v>
       </c>
     </row>
   </sheetData>
@@ -14199,22 +14199,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.06607434378451</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.74441680932428</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.30258620487769</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.49209111045028</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.20935434991681</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18.30357524565492</v>
+        <v>27.31340925253087</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.09283896603399</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.59338609163369</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.04214955275437</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.41211668832251</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.21226265634814</v>
       </c>
     </row>
   </sheetData>
@@ -14273,22 +14273,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.54157039367647</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.99326863963776</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.77584276438689</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.99109751234172</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.92817362576779</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.1624624973151</v>
+        <v>26.1500963009754</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.00449457109785</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.21798682375974</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.79968484491643</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.08765463991217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.37800728904443</v>
       </c>
     </row>
   </sheetData>
@@ -14347,22 +14347,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.27377217106356</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.94390997772959</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.48638491745184</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.6190960161105</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.59745116779193</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.65604090944937</v>
+        <v>36.30255433656854</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.59685932239951</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.72959129425723</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.95202354293668</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.65846695598354</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.65288189886855</v>
       </c>
     </row>
   </sheetData>
@@ -14421,22 +14421,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.74808679358416</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.94636250238205</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.65375619429235</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.49416277704875</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.1383582810971</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.30057480974204</v>
+        <v>30.4826479702162</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.07485789370903</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.73621889683547</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.58984588928832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.33905011607959</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.04637084856369</v>
       </c>
     </row>
   </sheetData>
@@ -14495,22 +14495,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.0328427633492</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.60026720141562</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.00743599120824</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.88701753549485</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.71665441033471</v>
-      </c>
-      <c r="G2" t="n">
-        <v>53.18917789576253</v>
+        <v>37.29424104445053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.8472069471223</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.80185272113589</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.53969670372538</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.77539539027855</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.293186330644</v>
       </c>
     </row>
   </sheetData>
@@ -14569,22 +14569,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.74401559667065</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.52071722363107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.66218511437452</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.80784158151602</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.61313341269495</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.74647735485</v>
+        <v>39.22564094309667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.49643544845352</v>
+      </c>
+      <c r="D2" t="n">
+        <v>52.03859044097959</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.62462082972319</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.77503078296877</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.57927004536857</v>
       </c>
     </row>
   </sheetData>
@@ -14643,22 +14643,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.22169958828989</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.36827667618226</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.68014255966853</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.19536019479322</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.27061476121902</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.41918385374922</v>
+        <v>30.27569941803414</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.66978982719779</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.48248085773149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.87215053449764</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.59493153056955</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.45529164446614</v>
       </c>
     </row>
   </sheetData>
@@ -14717,22 +14717,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.93099337571998</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.15518027522211</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.65098268046175</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.30828053754244</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.92493086651724</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.06238211648898</v>
+        <v>21.40727660122112</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.43840537089075</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.48763094355425</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.93673482311246</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.20434136367935</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.81572527433697</v>
       </c>
     </row>
   </sheetData>
@@ -14791,22 +14791,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.53553746205113</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.20622930555862</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.85137034288205</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.0195315582287</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.7412764638849</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.26931602873088</v>
+        <v>27.99579217121108</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.68993376465794</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.18159794738544</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.71217854767833</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.01293127148082</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.41157686320279</v>
       </c>
     </row>
   </sheetData>
@@ -14865,22 +14865,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.12386896336793</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.40781632648189</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.73411349997284</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.80768409813557</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.36676511174648</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.76939082245102</v>
+        <v>31.98080005739813</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.13033011853653</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.52964297881972</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.43554041888212</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.27725747794693</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.59459656679362</v>
       </c>
     </row>
   </sheetData>
@@ -14939,22 +14939,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.89046123024658</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.53069327281418</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.99319415736997</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.38800754021842</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.86382616745864</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.47965130507936</v>
+        <v>42.88516625703364</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.70968227065126</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.70780676655242</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.78566946675302</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.87566712758243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.6448562091316</v>
       </c>
     </row>
   </sheetData>
@@ -15013,22 +15013,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.73552957883783</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.62290784109712</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.58746776749198</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.91977841595667</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.91415247450534</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.88566292964575</v>
+        <v>27.32092948130849</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.53507348873999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.82633358103489</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.74085466379358</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.78631532844106</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.4253988199011</v>
       </c>
     </row>
   </sheetData>
@@ -15087,22 +15087,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.93455271281734</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.16597949853204</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.59304023466288</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.41012811142728</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.72383280683775</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.63950515484304</v>
+        <v>19.66999920938495</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.86936310058053</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.27915519700137</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.6440280083622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.47513760640495</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.55279575401312</v>
       </c>
     </row>
   </sheetData>
@@ -15161,22 +15161,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.84863290786133</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.67284984624738</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.26022492285496</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.24714755967322</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.80525677505535</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.65080345517712</v>
+        <v>36.66760321915982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.80413123603264</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.47200367983376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.95167592163028</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.66356046951181</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.36261680951988</v>
       </c>
     </row>
   </sheetData>
@@ -15235,22 +15235,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.8538332548739</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.64936126955115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.97385668437443</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.11222056194241</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.86524824029813</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.29916413806841</v>
+        <v>32.08991966807111</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.58895382347108</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.48454348402051</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.7602005325232</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.6517386512127</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.6594679948776</v>
       </c>
     </row>
   </sheetData>
@@ -15309,22 +15309,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.60130217873661</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.99311659720298</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.37698575185566</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.54282194758734</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.62140493824912</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.95397458784763</v>
+        <v>40.27562466083552</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.03575269984161</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.1460103824018</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.42508362074503</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.4238379356028</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.46329813046668</v>
       </c>
     </row>
   </sheetData>
@@ -15383,22 +15383,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.96065045773368</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.38431901798774</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.23374564864988</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.90086299712839</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.23690443489573</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.79025004439097</v>
+        <v>34.09001826330643</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.86212556848598</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.64792028562923</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.3826713164006</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.94851367536678</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.11416045530281</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
@@ -657,22 +657,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.08541819849162</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.98528890066206</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.95117069352023</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.5313765696454</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.6456021765115</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.04044378793501</v>
+        <v>37.64708086687398</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.25153079305326</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.66355788325921</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.82364242508375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.91921437072927</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.33695955039931</v>
       </c>
     </row>
   </sheetData>
@@ -731,22 +731,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.81327585454991</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.18209182292396</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.18465442381298</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.5520270427433</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.16423687396098</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.51999470387581</v>
+        <v>33.74372803214229</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.45445015007742</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.01463032787116</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.38296399508463</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.15408910655924</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.87702609082449</v>
       </c>
     </row>
   </sheetData>
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.41312294393639</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.38925396378113</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.03754351293132</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.38772742458494</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.19350376837788</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.63227880125322</v>
+        <v>25.84824507115042</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.53527084124602</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.08419084400996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.77144880210318</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.14382376943962</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.60480864111585</v>
       </c>
     </row>
   </sheetData>
@@ -879,22 +879,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.60136688251971</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.02462057059741</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.47994099926488</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.91111448592255</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.04760836361103</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.02525272881275</v>
+        <v>29.28123683937466</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.76204610366133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.71085844978021</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.13768308394872</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.74712211018003</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.44467026801355</v>
       </c>
     </row>
   </sheetData>
@@ -953,22 +953,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.85748187456914</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.06808223805803</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.75261304869947</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.22125797313405</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.92902728913585</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.07552765235396</v>
+        <v>31.83430476036412</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.83375673766153</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.11393939330472</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.53018934346108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.29426555348279</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.43070528589706</v>
       </c>
     </row>
   </sheetData>
@@ -1027,22 +1027,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.81041485980475</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.86942084874754</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.75256615372334</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.72707413609201</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.29695978076811</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.80719558919131</v>
+        <v>38.90331382746067</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.84467888619398</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.02201162952613</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.90970776963169</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.89588620582507</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.1012681848303</v>
       </c>
     </row>
   </sheetData>
@@ -1101,22 +1101,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.01761018163163</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.34243983485961</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.68660910743692</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.58709590477333</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.18131503255106</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.37400838991197</v>
+        <v>32.58983541521305</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.18012227081137</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.24653129104567</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.84584854238521</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.72104623547243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.0482037420493</v>
       </c>
     </row>
   </sheetData>
@@ -1175,22 +1175,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.85353243732421</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.55750741650719</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.97412580719715</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.73103162344123</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.22673135674131</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.72440976529158</v>
+        <v>27.74570295940557</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.83793094002915</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.49472520804174</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.00704973419096</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.75130793760662</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.63234971533118</v>
       </c>
     </row>
   </sheetData>
@@ -1249,22 +1249,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.94483621052103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.7640572622196</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.46644537934781</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.39423535467614</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.33978509344982</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.35209341806849</v>
+        <v>27.93500090567384</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.1038834673423</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.61274480791502</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.76466258343549</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.64468397286787</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.61806648963402</v>
       </c>
     </row>
   </sheetData>
@@ -1323,22 +1323,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.68970240758218</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.29240509666241</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.22060879991641</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.01569608085543</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.46650960250147</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.38693006946929</v>
+        <v>56.82526038158264</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.42373896464515</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.13418401105002</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.00481725582282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.84754504289897</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.52814580006952</v>
       </c>
     </row>
   </sheetData>
@@ -1397,22 +1397,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.37859668526741</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.7257940066344</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.47258756544977</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.80150777341134</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.82981720611932</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.94807903475966</v>
+        <v>30.1920925033836</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.89164711878518</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.48319371190346</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.55624143201052</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.54589904783171</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.08487171811006</v>
       </c>
     </row>
   </sheetData>
@@ -1471,22 +1471,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.16595374376585</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.22430905154766</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.13611900757557</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.39643983148162</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.34305229568677</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.56567051531788</v>
+        <v>36.43947952689285</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.20565589547938</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.92876508705309</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.74744597121427</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.80104508302996</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.11339093264917</v>
       </c>
     </row>
   </sheetData>
@@ -1545,22 +1545,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.16292761428067</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.33089903414259</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.01216560385143</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.24635950264695</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.96544984342292</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.44120718408546</v>
+        <v>28.27042844433724</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.21315676302378</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.04344692143919</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.57513519751575</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.95576577320111</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50.39937343056386</v>
       </c>
     </row>
   </sheetData>
@@ -1619,22 +1619,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.16877776744726</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.65566438718453</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.21910053150017</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.79289327772644</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.221987425189</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.34904029747084</v>
+        <v>40.01408431730857</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.83579461545613</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.31318495394183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.0065491038488</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.44832942209213</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.4153271522997</v>
       </c>
     </row>
   </sheetData>
@@ -1693,22 +1693,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.97001090011808</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.98682831394159</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.65220554143407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.84317208180362</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.57395702663291</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.90179660370741</v>
+        <v>27.79758476509508</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.32796233159551</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.862745706616</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.04288375532891</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.30872642148469</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.8495284641072</v>
       </c>
     </row>
   </sheetData>
@@ -1767,22 +1767,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.94536002916978</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.5561422822081</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.02504064927591</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.58453176378563</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.05030936581225</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.04076817566771</v>
+        <v>35.95943251141082</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.07433779970763</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.28764597189034</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.93095361459308</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.949036529328</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.90347086460532</v>
       </c>
     </row>
   </sheetData>
@@ -1841,22 +1841,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.61295141270322</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.88236756934304</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.04839631373977</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.44438346064491</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.81698011852068</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.99105830780575</v>
+        <v>30.63515713248304</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.66895114164792</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.4180382519178</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.00090537982602</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.49335071510355</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.68852337736705</v>
       </c>
     </row>
   </sheetData>
@@ -1915,22 +1915,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.37901583809413</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.00305354454139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.49491942338958</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.32130661521551</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.3681109463412</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.54163421533541</v>
+        <v>34.45413145039279</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.37901653008242</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.17027931641557</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.66790581780059</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.83897001203087</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.21255896294224</v>
       </c>
     </row>
   </sheetData>
@@ -1989,22 +1989,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.2466957239533</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.62143532396149</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.64064082234067</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.59577118242607</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.90289257604874</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.74159062555689</v>
+        <v>41.96002398626066</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.96163632131727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.8020015069964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.47044464105038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.74781427750123</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.10369109568937</v>
       </c>
     </row>
   </sheetData>
@@ -2063,22 +2063,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.86813749683888</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.33317978404921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.58101846116531</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.59878772932413</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.38365318154559</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.44556562585741</v>
+        <v>29.86354857842505</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.56948831336022</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.23606412617896</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.5594405487496</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.11431177958981</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.45009459737913</v>
       </c>
     </row>
   </sheetData>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.0515594079114</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.94808815268225</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.45697770191752</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.96178510796332</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.19791025154542</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.97010318492423</v>
+        <v>30.69144166640308</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.61270853596941</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.4048584192516</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.92866301807111</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.24477782812172</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.34778691047048</v>
       </c>
     </row>
   </sheetData>
@@ -2211,22 +2211,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.57774516688177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.7136187178802</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.695879428211</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.29521398561808</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.03400819434489</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.88512271667447</v>
+        <v>33.87067060761038</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.45270270637364</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.62954731787367</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.23219299657806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.39344668882137</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.75177052354998</v>
       </c>
     </row>
   </sheetData>
@@ -2285,22 +2285,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.67434298226899</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.50315075041607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.16062654396906</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.65978026341411</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.53230177667606</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.6662922828203</v>
+        <v>28.37348351058019</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.19305324673734</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.67453182717315</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.77706732122381</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.84814387446207</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.32655111362631</v>
       </c>
     </row>
   </sheetData>
@@ -2359,22 +2359,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.12742890873314</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.82499303226866</v>
-      </c>
-      <c r="D2" t="n">
-        <v>53.84746591154238</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.5045056084106</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.77152223199455</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.08794577153295</v>
+        <v>29.01718040562493</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.69703369429847</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.49679816180668</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.91378200913207</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.40765192243386</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48.12805378168889</v>
       </c>
     </row>
   </sheetData>
@@ -2433,22 +2433,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.7946884029392</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.34488302470817</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.26293975674842</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.95712139924993</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.65648442527586</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.45882651745434</v>
+        <v>39.70978133328337</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.76110460931752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.39265278924167</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.03416389592028</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.3491043927511</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.75663356165966</v>
       </c>
     </row>
   </sheetData>
@@ -2507,22 +2507,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.0176921556151</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.51516786477622</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.91757478989648</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.36706528504658</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.19146217153442</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.34131692510998</v>
+        <v>31.06324752211719</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.98501561032727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.43147080952891</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.98727102501151</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.00368616911408</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.66552750231104</v>
       </c>
     </row>
   </sheetData>
@@ -2581,22 +2581,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.95752663488058</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.99214146102322</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.04740007382991</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.84410865932207</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.40098221060979</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.05701927617793</v>
+        <v>33.72018979207841</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.95268884389763</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.27864243392564</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.37650203452415</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.81748375500677</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.68258744457206</v>
       </c>
     </row>
   </sheetData>
@@ -2655,22 +2655,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.09639146153275</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.2855575639517</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.70239745873126</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.76942965098254</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.54615604616694</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.0880144719457</v>
+        <v>28.8228387804904</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.18870162963892</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.71895491837617</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.26021819345051</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.07357549045673</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.75215524386373</v>
       </c>
     </row>
   </sheetData>
@@ -2729,22 +2729,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.70451012662148</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.68559244108865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.73242339889112</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.93389073422858</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.65253828650382</v>
-      </c>
-      <c r="G2" t="n">
-        <v>61.30308041849641</v>
+        <v>29.05757360513232</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.26955702519133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.02354410835121</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.25156024005216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.83271361878088</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.65248315608127</v>
       </c>
     </row>
   </sheetData>
@@ -2803,22 +2803,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.38791263504713</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.53787516108553</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.08761004874286</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.01143816416679</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.67540912241873</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.74708184228019</v>
+        <v>38.07646829935909</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.24656580872151</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.20581916235756</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.24048378176953</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.6958624156088</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.05572632542496</v>
       </c>
     </row>
   </sheetData>
@@ -2877,22 +2877,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.14315509143745</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.08231391572821</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.62876134774355</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.73530474556303</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.68835301533798</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.62196622035314</v>
+        <v>42.43894149736029</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.0640157002797</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.61679936719384</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.79980937568494</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.42983771300251</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.58452035382962</v>
       </c>
     </row>
   </sheetData>
@@ -2951,22 +2951,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.34378067097136</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.82687592979534</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.12693801968081</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.25607247305439</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.41818725997081</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.46525713218239</v>
+        <v>38.04783236495746</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.81650491335478</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.49723998197744</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.36007129886337</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.10627224030188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.50220988301594</v>
       </c>
     </row>
   </sheetData>
@@ -3025,22 +3025,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.88318930521924</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.53779922303432</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.76104431295344</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.95658116693208</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.68401550010197</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22.62647825381575</v>
+        <v>43.27335727946008</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.10895563555405</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.86649951305541</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.12278307779312</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.76868477595441</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.43931882876577</v>
       </c>
     </row>
   </sheetData>
@@ -3099,22 +3099,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.60793821287765</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.72144900719703</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.42150268090895</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.69293706875927</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.11348444536701</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.51992870594533</v>
+        <v>30.89483560368554</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.95906937164481</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.21103169069494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.68863670478315</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.24448189528423</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.49380409189293</v>
       </c>
     </row>
   </sheetData>
@@ -3173,22 +3173,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.14109832849951</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.57042255532067</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.1423436916057</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.13325239327093</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.86523794681494</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.27967794281236</v>
+        <v>29.29228572818095</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.69081588145889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.44679684034649</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.48348244129441</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.90199709516342</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.31258534298976</v>
       </c>
     </row>
   </sheetData>
@@ -3247,22 +3247,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.44516222214725</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.40970922750962</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.03217868131855</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.97826627297518</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.19544039554931</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.75664338075188</v>
+        <v>33.12523067902099</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.17278889437171</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.72005645602296</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.49196221476152</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.17608090651748</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.13958467511527</v>
       </c>
     </row>
   </sheetData>
@@ -3321,22 +3321,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.7339381482131</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.00124577784845</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.13646004951512</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.83358112384412</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.94557895659525</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.05704722882714</v>
+        <v>28.86545310896043</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.29368345367995</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.87815898354785</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.04333931717477</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.20569395851391</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.50081075081007</v>
       </c>
     </row>
   </sheetData>
@@ -3395,22 +3395,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.62735862711305</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.73043073013215</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.7215162623275</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.68125774962555</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.18487863230706</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.57006217813694</v>
+        <v>44.25480426808815</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.08471221196054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.13641353775296</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.98160803008824</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.14063488888867</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.53360579992276</v>
       </c>
     </row>
   </sheetData>
@@ -3469,22 +3469,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.97494889601055</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.62264468414833</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.6571783263787</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.79237051760838</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.20943897737114</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.23843752743036</v>
+        <v>27.36836297877324</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.47053396127218</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.38909107107261</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.56203106145198</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.31140065991319</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.67827041854243</v>
       </c>
     </row>
   </sheetData>
@@ -3543,22 +3543,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.24019393125207</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.78027747187448</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.16293550793589</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.82788743007579</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.66017529084369</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.52953040660132</v>
+        <v>45.07642133817833</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.37250801987564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.72740018194673</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.31425939386632</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.95790382351975</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.49465014768893</v>
       </c>
     </row>
   </sheetData>
@@ -3617,22 +3617,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.81477614655694</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.68515607585993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.30538331005132</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.62131686838803</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.20281845643776</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.11667123707639</v>
+        <v>38.74091006864359</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.26267077711573</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.32992525076661</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.15923629408897</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.8809833862019</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.5219373390367</v>
       </c>
     </row>
   </sheetData>
@@ -3691,22 +3691,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.43060259338354</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.18022419251021</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.64195141137749</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.32332862019327</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.99500740379901</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.07787391884749</v>
+        <v>26.91053568670079</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.33942847927675</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.7649614115873</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.26481811118973</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.69582865890929</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.61961950345221</v>
       </c>
     </row>
   </sheetData>
@@ -3765,22 +3765,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.9950165661235</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.23119822735638</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49.70042527570347</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.31124749321824</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.77815737577944</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.13545763275419</v>
+        <v>50.15196024843131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.83686278615806</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.92643779583111</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.84533912873547</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.9213518279149</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.98800911606665</v>
       </c>
     </row>
   </sheetData>
@@ -3839,22 +3839,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.87497145333383</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.90102368041948</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.02240536780912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.47504152576273</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.15920180233898</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.04566858504336</v>
+        <v>31.49948980476906</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.03497466167109</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.8929748157693</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.39532894325342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.89218628662598</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.54204310623211</v>
       </c>
     </row>
   </sheetData>
@@ -3913,22 +3913,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.70189238669239</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.60407365801023</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.15515142929353</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.31835989922641</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.26934389737564</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.89046402125648</v>
+        <v>41.07789028469141</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.66635210719428</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.13449946681713</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.07662081602978</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.30887610512331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.91138803980708</v>
       </c>
     </row>
   </sheetData>
@@ -3987,22 +3987,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.12747068355202</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.55655267110148</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.54685492041428</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.67037677390707</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.45351740926095</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.51066908412436</v>
+        <v>47.44439866719274</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.50224131983914</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.47069609030998</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.37613285512195</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.15068367563369</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.31576925484661</v>
       </c>
     </row>
   </sheetData>
@@ -4061,22 +4061,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.44190428627967</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.53644474226627</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.8537847737751</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.24313054125177</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.14731331534851</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.65842928527854</v>
+        <v>30.41789836784671</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.74770859901136</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.86761100058261</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.15150961700863</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.271010355261</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.05257290168019</v>
       </c>
     </row>
   </sheetData>
@@ -4135,22 +4135,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.36995551028348</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.8066257740548</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.22509711790444</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.36132593829639</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.30662556954653</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.91527632477461</v>
+        <v>28.17714417243387</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.30430410707088</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.15799464164576</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.96906299457038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.49440461165968</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.06807516089386</v>
       </c>
     </row>
   </sheetData>
@@ -4209,22 +4209,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.52208057293181</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.96281299828496</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.3271747751071</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.81614308791064</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.64955748586253</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.53103126427255</v>
+        <v>37.96805597046424</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.7940130103269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.03728696948276</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.40379946199567</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.79789447791573</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.10331646396506</v>
       </c>
     </row>
   </sheetData>
@@ -4283,22 +4283,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.76037642194245</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.46685769208112</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.20513925199834</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.62181207119654</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.25019175074666</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.89083647410837</v>
+        <v>31.61451719554189</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.10914132695594</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.54887196292285</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.63400899519233</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.93388465555567</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.34377172294293</v>
       </c>
     </row>
   </sheetData>
@@ -4357,22 +4357,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.06871074734821</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.64986475374604</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.77845155398497</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.30419231772603</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.50285228658891</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.55942584476126</v>
+        <v>31.88773656010532</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.14609054020967</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.06959253332068</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.03300541161371</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.90013352379925</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.57657450419051</v>
       </c>
     </row>
   </sheetData>
@@ -4431,22 +4431,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.88829671083604</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.56361927147956</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.14212458897407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.77852409328581</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.41112157398742</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.62105938465275</v>
+        <v>29.22151212504307</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.03019789551451</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.46049598371656</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.73288382974889</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.40235470735013</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.00686159388214</v>
       </c>
     </row>
   </sheetData>
@@ -4505,22 +4505,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.3775270064176</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.59258524725453</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.93629345606036</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.12413055360781</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.65966454515166</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.19986314092785</v>
+        <v>33.17889316170888</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.16063305608507</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.86722794119644</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.41843061256853</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.9425379336795</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.64734816411781</v>
       </c>
     </row>
   </sheetData>
@@ -4579,22 +4579,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.75127276065146</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.56900688642763</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.64840593217664</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.27232196208414</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.8245513163606</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.36982525171148</v>
+        <v>34.77111060188981</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.90242077705026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.70924503014413</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.55037436279603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.55910726904171</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.78393128633301</v>
       </c>
     </row>
   </sheetData>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.66129341367791</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.79708900142953</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.36445122136082</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.4967632243096</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.20381464115396</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.71668340376335</v>
+        <v>38.08307785838655</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.48860254381765</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.05646846953586</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.9251613986114</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.71390915840227</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.86458294600985</v>
       </c>
     </row>
   </sheetData>
@@ -4727,22 +4727,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.69029919589984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.72488122919012</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.07544499185154</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.70546203777968</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.75762087082803</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.89995899739356</v>
+        <v>27.36432056596035</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.20010653289162</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.88896379435791</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.95435052593481</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.09461746203814</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.98746123737028</v>
       </c>
     </row>
   </sheetData>
@@ -4801,22 +4801,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.7350168454844</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.83624566915585</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.28024688935874</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.96861637765473</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.6480817901356</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.17119397840342</v>
+        <v>32.96909298574107</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.06847919186687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.51332846103284</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.14270644003491</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.50033538375153</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.87188776423127</v>
       </c>
     </row>
   </sheetData>
@@ -4875,22 +4875,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.82703127575135</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.24810765650919</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.33950206812433</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.1465224165493</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.81992003305474</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.07406193838241</v>
+        <v>30.05450251475409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.78600843567495</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.122817980641</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.62631861300122</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.37903908595461</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.72917481476868</v>
       </c>
     </row>
   </sheetData>
@@ -4949,22 +4949,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.69942599312815</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.56697881185003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.18453057626893</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.05010904606122</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.10224720596623</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.94319870978761</v>
+        <v>31.53055809714178</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.71980622256297</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.91016826373669</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.83113912851916</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51.97817647970589</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.68733822273237</v>
       </c>
     </row>
   </sheetData>
@@ -5023,22 +5023,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.9078500101997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.93133435790643</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.22901550942101</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.08962198711647</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.73371409211148</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.85269658155185</v>
+        <v>38.84880597376652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.03765637415083</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.84103633479346</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.95894231697057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.3461061574812</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.08375826974297</v>
       </c>
     </row>
   </sheetData>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.6546362117953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.54259521443576</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.12779262299976</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.95027486637117</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.03124473121575</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.31652744178243</v>
+        <v>34.82721024586652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.09387716835429</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.94249278916429</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.92456613399479</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.52724122828764</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.62872405555772</v>
       </c>
     </row>
   </sheetData>
@@ -5171,22 +5171,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.82084116102014</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.55630815811345</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49.85167123922883</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.9955885214988</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.29729920491335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.04299626898744</v>
+        <v>39.26578306039246</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.18154811459381</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.96111750449277</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.64797964430865</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.62213121855994</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.65758014360446</v>
       </c>
     </row>
   </sheetData>
@@ -5245,22 +5245,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.24436423723626</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.31883292549949</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.78967779417047</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.28704310335457</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.69680053079477</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.2188246741534</v>
+        <v>28.91566056185811</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.08391576095302</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.24592274705011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.68246975949487</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.76366491008696</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.02002966224366</v>
       </c>
     </row>
   </sheetData>
@@ -5319,22 +5319,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.75009254905533</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.46794983073437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.71945910550173</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.79017677583764</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.91302892570046</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.92809592875794</v>
+        <v>26.4716353213829</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.56261929495691</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.06919251342038</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.69072550939702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.8963517032726</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.9564404418526</v>
       </c>
     </row>
   </sheetData>
@@ -5393,22 +5393,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.58881030605184</v>
-      </c>
-      <c r="C2" t="n">
-        <v>60.96612468884798</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.93891636384131</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.90086528068228</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.27205689483442</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.4185062055609</v>
+        <v>41.0536422558321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.24543175729993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.59545645443757</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51.36649243407003</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.78804503976023</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.09038152053275</v>
       </c>
     </row>
   </sheetData>
@@ -5467,22 +5467,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.06285309848935</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.52913662175278</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.3288557925237</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.76025262882867</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.2373443531435</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.96965495162594</v>
+        <v>32.10230671832552</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.15020407426054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.22945723007233</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.38172370602209</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.93723869186362</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.86831063375184</v>
       </c>
     </row>
   </sheetData>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.87805560084485</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.81086411784721</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.94039784817664</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.26208601429046</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.98725148453085</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.3493825371125</v>
+        <v>38.69848925719359</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.52330848247652</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.84939808596791</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.35412548071861</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.58812471619692</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.09691151626109</v>
       </c>
     </row>
   </sheetData>
@@ -5615,22 +5615,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.6776597558127</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.45190778413107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.11496326192974</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.92039663581749</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.10758889092617</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.61272729429601</v>
+        <v>29.34864801680077</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.06373204917051</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.23381021927795</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.14185034642764</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.52826025518299</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.61185951638986</v>
       </c>
     </row>
   </sheetData>
@@ -5689,22 +5689,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.70226250366204</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.20370906957159</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.9734256262983</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.32266093723614</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.53273862460713</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.11045673363622</v>
+        <v>32.63707511234065</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.12179845941336</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.66588417496316</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.20703740714859</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.8989909515683</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.80259436234245</v>
       </c>
     </row>
   </sheetData>
@@ -5763,22 +5763,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.58561883490817</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.55256175373761</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.89578052228575</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.95883874757736</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.91494018413471</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.1500207705175</v>
+        <v>38.68521349674467</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.4640800599406</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.77398285855066</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.16689260508699</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.36531526373501</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.86293434768908</v>
       </c>
     </row>
   </sheetData>
@@ -5837,22 +5837,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.95601054933652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.0535828055223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.13821376754981</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.29329386351202</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.56595720987325</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.33078064253424</v>
+        <v>36.45130648239156</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.94017917775562</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.98055578233481</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.34749391857856</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.90283996218805</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.61706302918626</v>
       </c>
     </row>
   </sheetData>
@@ -5911,22 +5911,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.3684151982037</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.82009018664599</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.21078045264006</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.35085554541194</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.35132737192396</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.38834595258377</v>
+        <v>35.64544333684012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.70251718992195</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.44709853286517</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.84036364710468</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.58113287221317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.90938545006976</v>
       </c>
     </row>
   </sheetData>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.19549620832146</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.93525351029028</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.18316390345395</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.137913333378</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.99402469391114</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.08787351232509</v>
+        <v>42.65239297739171</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.4028559633705</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.38174191400336</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.61821231526461</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.14633631823401</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.2488441724524</v>
       </c>
     </row>
   </sheetData>
@@ -6059,22 +6059,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.2888204837658</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.36693211050375</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.60428122582115</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.06035843907458</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.54559971657217</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.28051791072468</v>
+        <v>32.39582098682558</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.66079978072846</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.21845509243511</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.94337447761409</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.1995589552714</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.03649592235174</v>
       </c>
     </row>
   </sheetData>
@@ -6133,22 +6133,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.65458863735388</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.83399552291993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.39446138757954</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.28442384863127</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.72138244226224</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.02443624955173</v>
+        <v>32.74813507419432</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.59833752065778</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.53096004571676</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.66896968369918</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.05447111002605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.82691646934847</v>
       </c>
     </row>
   </sheetData>
@@ -6207,22 +6207,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.30953334565511</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.57465680771521</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.73883293236329</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.11662164603943</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.5626784286003</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.14212755794852</v>
+        <v>37.25087011699237</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.28084719139748</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.24455718161598</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.50412166760853</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.90701984709639</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.98979970476726</v>
       </c>
     </row>
   </sheetData>
@@ -6281,22 +6281,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.13505768002114</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.83752633574184</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.12372493118646</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.44983848082678</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.36716288982878</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.53559215682524</v>
+        <v>48.46938606260024</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.21906954393404</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.59200477595081</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.51627581381257</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.91096802779237</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.74201946766433</v>
       </c>
     </row>
   </sheetData>
@@ -6355,22 +6355,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.05228127044525</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.4184635627869</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.60357006479217</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.12692307105305</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.10311845397058</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.64618970903965</v>
+        <v>25.73606010595697</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.71991514639571</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.54049497575408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.12905413916945</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.33192730893379</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.95857564708574</v>
       </c>
     </row>
   </sheetData>
@@ -6429,22 +6429,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.61225563439685</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.14142629732084</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.58367900457942</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.2425478278526</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.8935084836741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.76923073637813</v>
+        <v>21.35777654000438</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.49206291277652</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.17793659556931</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.57903612315049</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.54528552705665</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.73001292264149</v>
       </c>
     </row>
   </sheetData>
@@ -6503,22 +6503,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.61399168224047</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.44499498857788</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.0696703501206</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.75784311114189</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.86835766712531</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.58882262433173</v>
+        <v>35.55905284685177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.13390420084081</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.73212430069329</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.84964957950989</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.64109364551373</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.98672283218316</v>
       </c>
     </row>
   </sheetData>
@@ -6577,22 +6577,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.0287294582587</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.37613959960736</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.88150341117979</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.87396178976702</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.0113266398624</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.98046645051663</v>
+        <v>29.38607323238631</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.32279338165176</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.18768476137407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.30301326929595</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.17424631581214</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.68330567808614</v>
       </c>
     </row>
   </sheetData>
@@ -6651,22 +6651,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.84205619724896</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.87067396901422</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.48944383545289</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.39481945732776</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.84346921235142</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.9389077263648</v>
+        <v>31.59608996569983</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.76222568758642</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.00812975913157</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.79933949630655</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.60297732316164</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.70533485144945</v>
       </c>
     </row>
   </sheetData>
@@ -6725,22 +6725,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.71249803126254</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.97084733736144</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.32897508565409</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.93830511967634</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.41731638069907</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.82137415188501</v>
+        <v>36.8908494535313</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.18784582442198</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.49910045670076</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.84816467453272</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.96898822992019</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.0373622374913</v>
       </c>
     </row>
   </sheetData>
@@ -6799,22 +6799,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23159607130088</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.92257375415139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.72347084183833</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.88639382505371</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.74982434256512</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.28183654379566</v>
+        <v>37.13333058082564</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.27953705473207</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.77076853865783</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.35447300832809</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.88784637868778</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.4227776424879</v>
       </c>
     </row>
   </sheetData>
@@ -6873,22 +6873,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.32671809111525</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.02194703795843</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.54724469813901</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.74669368714049</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.22208824703811</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.57947525801761</v>
+        <v>21.01731137366244</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.08022376211788</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.48528684824812</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.79322634958388</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.10240825017147</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.16604391404486</v>
       </c>
     </row>
   </sheetData>
@@ -6947,22 +6947,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.10465992980312</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.86769558563572</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.84383334983725</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.97167098156189</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.3634921983456</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.74427417818862</v>
+        <v>35.12623150908201</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.94029677149387</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.70188477671071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.89118371264305</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.69747934825064</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.09908434190091</v>
       </c>
     </row>
   </sheetData>
@@ -7021,22 +7021,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.94106987649134</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.28042675034543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.72236076543273</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.46468563048041</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.52958093406045</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.00325065129087</v>
+        <v>29.85527820477039</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.39817709823866</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.90180774266841</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.85692175559622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.61155470682792</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.36836791040802</v>
       </c>
     </row>
   </sheetData>
@@ -7095,22 +7095,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.27617002625037</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.55932780049999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.3927880279053</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.34325471999104</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.37018905803432</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.43100170616452</v>
+        <v>32.44666239402628</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.51329921760557</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.28788468809902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.8704452831241</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.23963563318298</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.18302471781496</v>
       </c>
     </row>
   </sheetData>
@@ -7169,22 +7169,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.74341466091793</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.02125943585916</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.13412114326538</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19.89615705864523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.87667608643974</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.56961387578334</v>
+        <v>25.23162129991795</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.81254655049474</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.19773200134325</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.8749496995045</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.78540287352727</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.69137511892081</v>
       </c>
     </row>
   </sheetData>
@@ -7243,22 +7243,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.71678127628696</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.15900611283443</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.73702715644274</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.51105552268661</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.28998308308463</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.1761599578434</v>
+        <v>34.8426383372104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.3182564465445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.19251274847131</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.12355454363696</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.42768550352779</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.372798514403</v>
       </c>
     </row>
   </sheetData>
@@ -7317,22 +7317,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.95005102170622</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.20231140381743</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.34917129238445</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.77772994023428</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.04259505704916</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.96775010167092</v>
+        <v>32.97828858972252</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.27077118189259</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.05090788467605</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.98034276124355</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.55386126721154</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.04836675819497</v>
       </c>
     </row>
   </sheetData>
@@ -7391,22 +7391,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.40830788816728</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.61501288413133</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.41065526649383</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.06988381939727</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.80177397680288</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.62949687681211</v>
+        <v>33.88823017662961</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.41967486835348</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.02134981790887</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.1687438270082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.03402862951943</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.94462408410873</v>
       </c>
     </row>
   </sheetData>
@@ -7465,22 +7465,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.92002239542994</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.98187147026636</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.35085778566376</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.08656685836132</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.5966212493568</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.87876085433992</v>
+        <v>34.60924110095816</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.96823174245331</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.90882428610448</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.75279241570728</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.29735409847189</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.81835941785899</v>
       </c>
     </row>
   </sheetData>
@@ -7539,22 +7539,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.22240889432835</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.96262462018982</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.82535530241649</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.70453703311572</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.06529104614157</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.19489789491233</v>
+        <v>35.29999475972581</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.51985284483273</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.87139968588139</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.20536812623172</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.70390538939645</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.45666520717356</v>
       </c>
     </row>
   </sheetData>
@@ -7613,22 +7613,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.15402661143965</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.29851863934461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.06877190305442</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.59536920640757</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.01382455571805</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.80995017322897</v>
+        <v>29.98376505098502</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.81147816388146</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.75213529657805</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.36623882529312</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.49409555896214</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.85468950238547</v>
       </c>
     </row>
   </sheetData>
@@ -7687,22 +7687,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.54750666222281</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.9524954055486</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.77149652728625</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.79825287515259</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.45680002312673</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.05156753611958</v>
+        <v>25.56296039844641</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.75361794797009</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.86471515816273</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.83337967457514</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.31599079979388</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.48527001862682</v>
       </c>
     </row>
   </sheetData>
@@ -7761,22 +7761,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.66129508557383</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.78498103511765</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.29484450507246</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.45550939556398</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.05267113651866</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.92527419335462</v>
+        <v>35.91458526138687</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.9208952311194</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.13379575971114</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.38496710290673</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.25184956850533</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.01335303269927</v>
       </c>
     </row>
   </sheetData>
@@ -7835,22 +7835,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.45971409914834</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.49304169594039</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.13796823817407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.8021225660332</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.45711477864217</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.70985378714744</v>
+        <v>50.48023040055035</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.70510641152604</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.3738776955704</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.31195737599669</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.38596279243481</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.71704061728456</v>
       </c>
     </row>
   </sheetData>
@@ -7909,22 +7909,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.80875115204626</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.07744410935389</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.72888274357857</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.75876988620166</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.53050336629122</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.51278039467532</v>
+        <v>51.88179031943081</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.03939668876188</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.51454852553557</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.80938689397445</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.46653707986028</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.1201787436336</v>
       </c>
     </row>
   </sheetData>
@@ -7983,22 +7983,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.73302177763177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.3793082731595</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.65142424889407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.0475553490123</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.71802371189844</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.27982476785482</v>
+        <v>31.86131247006546</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.07275834178246</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.19582580893179</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.15824317947215</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.0720757766605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.86697915205316</v>
       </c>
     </row>
   </sheetData>
@@ -8057,22 +8057,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.16483643655506</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.32122974864336</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.90330034853795</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.8104250591256</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.2721789255707</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.80977235501767</v>
+        <v>35.71493005535339</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.84872662229604</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.48956585557045</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.46150116772103</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.19007623596172</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.07839813551228</v>
       </c>
     </row>
   </sheetData>
@@ -8131,22 +8131,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.91029366698994</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.88379243110005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.27809423950048</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.53768050733477</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.92042392036219</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.69328471962812</v>
+        <v>30.31253682718445</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.42945495575577</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.45701043310839</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.68312732973001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.85168807560671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.8971533870169</v>
       </c>
     </row>
   </sheetData>
@@ -8205,22 +8205,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.01435502668637</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.91687942820437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.39467248274232</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.32392563617769</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.15126119253897</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.2298298791867</v>
+        <v>29.3846513840592</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.87116606643743</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.59815011520706</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.71963579250382</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.75307419123278</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.57704060736396</v>
       </c>
     </row>
   </sheetData>
@@ -8279,22 +8279,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.55461592708128</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.6276406258221</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.65726911217319</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.72855878173577</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.68434629157855</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.18536231854364</v>
+        <v>42.49415026765078</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.30257067860277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.06478605881613</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.50356090617221</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.61928574176894</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.10175714444368</v>
       </c>
     </row>
   </sheetData>
@@ -8353,22 +8353,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.37886869189861</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.48022592959826</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.87363922067187</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.69158711805566</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.03575475276507</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.94212259770629</v>
+        <v>37.35911230733595</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.22591278272296</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.50156392483184</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.68383303421326</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.73272198717812</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.21410995760387</v>
       </c>
     </row>
   </sheetData>
@@ -8427,22 +8427,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.18629092058805</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.58400272405097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.22743048658116</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.57554232795798</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.46421924428737</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.89521867092992</v>
+        <v>41.13721367287376</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.93213461333709</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.57737033035123</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.89773548428389</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.26358953784349</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.30718631592152</v>
       </c>
     </row>
   </sheetData>
@@ -8501,22 +8501,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.3503866907578</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.13368784908171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.75299367284067</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.36362511717938</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.78126895519745</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.62908734334692</v>
+        <v>30.55396839393284</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50.29399052517957</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.28841775676748</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.65374103219716</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.34155322142382</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.94545323532065</v>
       </c>
     </row>
   </sheetData>
@@ -8575,22 +8575,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.67788630697969</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.283834914862</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.61547065035624</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.03812011582029</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.98782811175833</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.39201782179338</v>
+        <v>37.25616886291525</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.38851973198905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.30272730218346</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.00961134703639</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20.93092054652521</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.99702718795905</v>
       </c>
     </row>
   </sheetData>
@@ -8649,22 +8649,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.25385531722047</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.80094071441273</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.57581608130449</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.04944340504694</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.49691966415623</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.52486467812038</v>
+        <v>29.252495061201</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.08344428502863</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.85692789363711</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.42689230487852</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.66370594905806</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.58918266755196</v>
       </c>
     </row>
   </sheetData>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.48478938752297</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.01189607146061</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.75678920288912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.30588104348844</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.17869294370604</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.55539287795549</v>
+        <v>39.97951032973708</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.68773106664745</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.15784665155174</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.52553912990979</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.21225818951986</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.25330845550242</v>
       </c>
     </row>
   </sheetData>
@@ -8797,22 +8797,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.17073113178593</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.42590893250107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.70536156763242</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.0601229181724</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.79831673782899</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.62122068923618</v>
+        <v>37.99134475437817</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.60118112892371</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.50359981095838</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.06387027394277</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.8202338142975</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.57319619680768</v>
       </c>
     </row>
   </sheetData>
@@ -8871,22 +8871,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.56360119439712</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.6151123100737</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.56710547933547</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.64636091696228</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.29939147893424</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.95506137092799</v>
+        <v>34.69636412958256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.28847365734796</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.81227690951007</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.80396204985443</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.23333112209549</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.5568504517627</v>
       </c>
     </row>
   </sheetData>
@@ -8945,22 +8945,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.47658474652372</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.3633424705687</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.80998218676114</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.46267995422973</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.7281693017656</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.70525892544394</v>
+        <v>31.38755286724468</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.00059393765129</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.32220654392157</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.95556660468515</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.32349501112668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.39747766752298</v>
       </c>
     </row>
   </sheetData>
@@ -9019,22 +9019,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.75685615541501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.69240833116289</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.13495414375203</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.691255133603</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.38719628492945</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.40999178408636</v>
+        <v>32.42800018442998</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.38044828513132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.07982287499097</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.95690555613716</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.01986573683158</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.49863819953446</v>
       </c>
     </row>
   </sheetData>
@@ -9093,22 +9093,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.22004781451245</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.99465859620761</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.6566195380761</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.42936115717433</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.12068796555299</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.46131101940848</v>
+        <v>29.24733957986667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.02150499305764</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.11016240673673</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.46800924303444</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.51628420928805</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.79100952613331</v>
       </c>
     </row>
   </sheetData>
@@ -9167,22 +9167,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.38444954257583</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.87019860018642</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.40967994677487</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.03468883913095</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.20163822672789</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.5665348987508</v>
+        <v>25.6610486973741</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.30006541806438</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.39720321835803</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.11801573243724</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.37447893229364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.61135539790696</v>
       </c>
     </row>
   </sheetData>
@@ -9241,22 +9241,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.63390930773118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.42145255369747</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.01676739348685</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.26067845047145</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.60364171080634</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.4781754894616</v>
+        <v>30.90570633139435</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.42079441429749</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.97426253003631</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.55472536993143</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.57966504563317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.41943474196154</v>
       </c>
     </row>
   </sheetData>
@@ -9315,22 +9315,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.12553106790132</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.92783096305564</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.79980105306755</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.98112241620984</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.91967166475651</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.47941178382824</v>
+        <v>36.52037614228161</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.56070273971192</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.26881957055389</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.20512230983432</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.01910931953703</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.97118950071052</v>
       </c>
     </row>
   </sheetData>
@@ -9389,22 +9389,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.03011178904736</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.95263530210396</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.80942996400712</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.7569774814434</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.25260568213535</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.15076905311432</v>
+        <v>27.25643047944756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.25697469352464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.12027143202953</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.51682004177903</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.81232193223024</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.11710452364099</v>
       </c>
     </row>
   </sheetData>
@@ -9463,22 +9463,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.88309891629861</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.57225741377907</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.28318793766984</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.10858115522598</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.81705903766662</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.82271185849104</v>
+        <v>53.28898782780885</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.83299637759665</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.7544177874378</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.61238036822478</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.71874231618473</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.67469870779742</v>
       </c>
     </row>
   </sheetData>
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.55297442578177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.18681190590996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.93934236098944</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.92809471211131</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.94920051821035</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.25870003614282</v>
+        <v>34.30683096423528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.12923952044785</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.49986586841922</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.69382499256604</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.56055600934021</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.19448666439061</v>
       </c>
     </row>
   </sheetData>
@@ -9611,22 +9611,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.76787299819279</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.81607471992286</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.77509819006398</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.63489817207474</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.69234360196975</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.61536112368932</v>
+        <v>39.85882458991897</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.25918081055711</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.48509656686689</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.57069956652889</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.59387680653839</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.67218129945585</v>
       </c>
     </row>
   </sheetData>
@@ -9685,22 +9685,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.61881719296352</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.59594163621239</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.38505103261613</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.51684687416838</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.80697484677444</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.04002759565522</v>
+        <v>28.82421296536273</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.32930653033831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.35603333477535</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.27526249426428</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.16470725018425</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.35284825851667</v>
       </c>
     </row>
   </sheetData>
@@ -9759,22 +9759,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.70888684408261</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.49048653095235</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.27131635066529</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.2911360649038</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.41190286443161</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.21192138631524</v>
+        <v>23.1028060204091</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.22167534680257</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.33132823033382</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.8923770875057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.06766432000614</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.09099421709288</v>
       </c>
     </row>
   </sheetData>
@@ -9833,22 +9833,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.65448203243242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.65942265544044</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.06759720285408</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.3602852820619</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.91146149093891</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.78043469670365</v>
+        <v>29.9270635047558</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.86060846435524</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.83021711697204</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.696957694728</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.98828807413925</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.65631933393259</v>
       </c>
     </row>
   </sheetData>
@@ -9907,22 +9907,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.3003012689092</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.15974067987602</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.86570101011176</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.92959858132426</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.28674630909524</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.97152340827686</v>
+        <v>32.00442687528001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.21043286030523</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.56337140222651</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.50260414786244</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.80068751396989</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.24217468783794</v>
       </c>
     </row>
   </sheetData>
@@ -9981,22 +9981,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.19714537733299</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.75050654795047</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.47828382306027</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.42135488719137</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.92520978093983</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.60947169162606</v>
+        <v>25.98207479935484</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.01580958788776</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.59391612105175</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.14699532832118</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.49624315515139</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.14877233912753</v>
       </c>
     </row>
   </sheetData>
@@ -10055,22 +10055,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.45398939053131</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.56174100334315</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.74057631666302</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.73601705976193</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.78204528140067</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.76052696124771</v>
+        <v>35.83087604633683</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.93529639429065</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.68897264028428</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.57760835408651</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.62060914661994</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.08170594802498</v>
       </c>
     </row>
   </sheetData>
@@ -10129,22 +10129,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.48222467468864</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.60795469567884</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.55126559919078</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.21740210570003</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.7741549193904</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.22509862732166</v>
+        <v>26.59764851857664</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.12613415207734</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.71025379277182</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.17046617577235</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.22715092343027</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.1061624028796</v>
       </c>
     </row>
   </sheetData>
@@ -10203,22 +10203,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.05882183258849</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.45184182273097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.76115848880882</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.1515188953756</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.05696138903537</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.27967665504157</v>
+        <v>31.95583582383813</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.25574781494132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.02727174649188</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.95078158231625</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.1322752033884</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.25360494910477</v>
       </c>
     </row>
   </sheetData>
@@ -10277,22 +10277,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.8522260664173</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.48963265485632</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.62523166927532</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.66272972789586</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.8338082118882</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.15697171291927</v>
+        <v>28.26170827586231</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.24755001617601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.24242077032888</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.18120810448436</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.75892302780272</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.31349815064544</v>
       </c>
     </row>
   </sheetData>
@@ -10351,22 +10351,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.92829471149156</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.4697643880662</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.58558432612998</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.9356833554333</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.28838544464849</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.18622288936268</v>
+        <v>32.63177018480032</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.01366588265545</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.17290237027243</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.70995187956195</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.54437302006109</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.70280848629456</v>
       </c>
     </row>
   </sheetData>
@@ -10425,22 +10425,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.23865109024154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.24485157226231</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.63973569885494</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.43870663619531</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.78710075707824</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.20621224537463</v>
+        <v>27.82376953974028</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.47034148474945</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.61314444069827</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.3533910382175</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.5225287258915</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.96709309520041</v>
       </c>
     </row>
   </sheetData>
@@ -10499,22 +10499,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.19756584380114</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.20459861335648</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.46482943666668</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.42618877887549</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.86051575729958</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.76463672059486</v>
+        <v>29.94092549887194</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.05472106800132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.98774097882066</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.07768424552417</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.5049994470229</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.50502723567547</v>
       </c>
     </row>
   </sheetData>
@@ -10573,22 +10573,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.59662836814764</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.20662713805999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.27487557358914</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.80035940178476</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.52867762064842</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.54290236712551</v>
+        <v>47.79607274326483</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.03441466377672</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.39385695219891</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.68644466315169</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.33708276824766</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.12252835170706</v>
       </c>
     </row>
   </sheetData>
@@ -10647,22 +10647,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.55501379230969</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.78499342015055</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.18918048513198</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.94681632094214</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.33418690967584</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.27522616450224</v>
+        <v>46.16041330796976</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.28791935450359</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.1593308295671</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.32889305351001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.89955443203827</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.64359887689574</v>
       </c>
     </row>
   </sheetData>
@@ -10721,22 +10721,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.50333316237576</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.01668763950244</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.06551118675879</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.13877320607859</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.34881494333708</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.78739353041604</v>
+        <v>45.75508052541143</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.50148334759741</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.7052811477392</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.57116545035188</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.69921272736435</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.91376656022015</v>
       </c>
     </row>
   </sheetData>
@@ -10795,22 +10795,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.42844688069902</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.23141300246485</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.39576486151128</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.26860865239444</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.34943047204212</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.13952064175763</v>
+        <v>29.95984504675537</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.83819776649445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.61640716627093</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.78407900933071</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.68688223880895</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.32416465858392</v>
       </c>
     </row>
   </sheetData>
@@ -10869,22 +10869,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.97113402945381</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.28390596391339</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.50914834903573</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.78417141882961</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.28262914539023</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.88932434364594</v>
+        <v>32.5989483654362</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.53892734260188</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.19632946055181</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.76992412599713</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.07348455359891</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.41694863664635</v>
       </c>
     </row>
   </sheetData>
@@ -10943,22 +10943,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.3478875328512</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.81633479683251</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.22538853539677</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.90767751053912</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.4490245450058</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.60889804924123</v>
+        <v>30.59156528875598</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48.08742232103735</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.21185738983151</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.1142802420948</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.17529704852965</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.01928054604537</v>
       </c>
     </row>
   </sheetData>
@@ -11017,22 +11017,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.06662444455056</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.00975095745195</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.58270837771244</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.82988948998474</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.90444015403808</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.36716190103634</v>
+        <v>37.95140106793323</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.83486803938709</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.52100451322903</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.26834297037635</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.86544407051931</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.79320368673385</v>
       </c>
     </row>
   </sheetData>
@@ -11091,22 +11091,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.66065340698557</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.23716870324612</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.73062400002742</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.49415578304993</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.3007760400186</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.36223758616517</v>
+        <v>30.06417938382056</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.30173941813039</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.43919747857208</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.41415325095068</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.76404139361638</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.29220447832811</v>
       </c>
     </row>
   </sheetData>
@@ -11165,22 +11165,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.49717677491792</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.6620143103576</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.21284879438173</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.47502195889327</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.86674789557705</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.47456517245718</v>
+        <v>26.23378117742092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.82032714211048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.51483125760023</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.28156427108135</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.1911908268245</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.12065370887923</v>
       </c>
     </row>
   </sheetData>
@@ -11239,22 +11239,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.05382526789582</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.96985904044401</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.75213273318321</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.71343689228179</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.40299570167766</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.15525981775339</v>
+        <v>33.48225196079177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.9919238603144</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.28331104805437</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.41100425000584</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.92990654817393</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.85378583866953</v>
       </c>
     </row>
   </sheetData>
@@ -11313,22 +11313,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.59882522528177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.9146568568034</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.08853568023824</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.94232348151027</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.16853936564893</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.03982023337876</v>
+        <v>31.55801954270376</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.86541805432627</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.78188303427097</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.26516518617847</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.67847935231494</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.08980012965201</v>
       </c>
     </row>
   </sheetData>
@@ -11387,22 +11387,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.9570945144574</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.2318265622486</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.88269512408285</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.60676502841622</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.82602034915766</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.30132044711622</v>
+        <v>25.77657660201886</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.31876760942308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.53594643126996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.32424858546701</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.46841100724286</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.08738855028712</v>
       </c>
     </row>
   </sheetData>
@@ -11461,22 +11461,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.16058993840176</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.1798959991355</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.20940382370008</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.04866801042092</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.9030522718806</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.16946978521319</v>
+        <v>37.48651082619496</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.39017018066948</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.43489355027113</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.36555673341521</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.93981477892805</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.7967273092203</v>
       </c>
     </row>
   </sheetData>
@@ -11535,22 +11535,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.71597020393326</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.35870422387602</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.42089619759209</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.27881363589003</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.2035384118789</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.50663828066313</v>
+        <v>33.97983165843152</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.02014801574098</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.84866403474142</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.69159953771046</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.56687030412921</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.6299791693209</v>
       </c>
     </row>
   </sheetData>
@@ -11609,22 +11609,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.03290998981296</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.27694677168563</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.62824313315529</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.83024437867297</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.67559179403939</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.26046881874042</v>
+        <v>40.53489278703321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.46470266354916</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.21567096108192</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.96037910602328</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.79488644394653</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.35447133352131</v>
       </c>
     </row>
   </sheetData>
@@ -11683,22 +11683,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.02992571139968</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.75204572917282</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.61982438703928</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.81513788004249</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.07689461601659</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.66217492909659</v>
+        <v>29.83352074001464</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.3395836735685</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.2274726573184</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.64693344924477</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.94016107793131</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.44399122376258</v>
       </c>
     </row>
   </sheetData>
@@ -11757,22 +11757,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.9139293919518</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.65984602569243</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.43606922839884</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.05192970019559</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.63441043783379</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.1216120739311</v>
+        <v>29.92343128267736</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.44758839853871</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.47333984159506</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.74615962891398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.90497843876075</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.84189497972027</v>
       </c>
     </row>
   </sheetData>
@@ -11831,22 +11831,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.26117953037295</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.44148134011236</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.35282307004408</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.05846227695876</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.09444984775645</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.56504855531232</v>
+        <v>28.32015707514498</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.78692289929551</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.25376897596667</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.48542657948055</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.53357032600929</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.82222981660269</v>
       </c>
     </row>
   </sheetData>
@@ -11905,22 +11905,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.81128752079946</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.06171118757766</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.10723404319344</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.19518490388136</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.40972871258656</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.03192845970149</v>
+        <v>30.14767735890248</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.89021677215262</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.49613260502136</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.35676432448587</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.10012581167219</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.0617301125354</v>
       </c>
     </row>
   </sheetData>
@@ -11979,22 +11979,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.61985784844012</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.72944567625364</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.45093222318509</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.42867928848124</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.26929438238388</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.29709842533919</v>
+        <v>26.63884007411616</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.11963630157329</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.45330267773475</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.92412009942568</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.01219812981277</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.49095719261307</v>
       </c>
     </row>
   </sheetData>
@@ -12053,22 +12053,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.82984518698572</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.62343658779861</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.24875947047252</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.09375466595917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.95928124507881</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.21479572723725</v>
+        <v>37.80554743610915</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.62955080244749</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.08766743362155</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.5446475127339</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.03290735349118</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.3959038259743</v>
       </c>
     </row>
   </sheetData>
@@ -12127,22 +12127,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.57212765652781</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.02327500697324</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.82010701955146</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.47654365862251</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.27653077133343</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.89259250351461</v>
+        <v>29.9255054384195</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.81880036294081</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.07437115553911</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.72857163041519</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.89254450575908</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.78624706473073</v>
       </c>
     </row>
   </sheetData>
@@ -12201,22 +12201,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.60525616759508</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.84960504502772</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.69743420802537</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.27854019647736</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.27727246006335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.50524496904913</v>
+        <v>38.44414650059767</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.22538585376529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.20196448603595</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.99957866900712</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.74660325001393</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.20816948310021</v>
       </c>
     </row>
   </sheetData>
@@ -12275,22 +12275,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.10967747524654</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.62138153096877</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.00757284981335</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.44599164015972</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.43395739573358</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.55060245478789</v>
+        <v>25.03567620720854</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.26483881666645</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.55172232903428</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.70343748244346</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.8888093569126</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.50154151293198</v>
       </c>
     </row>
   </sheetData>
@@ -12349,22 +12349,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.30098901666373</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.87140075767529</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.72650909359426</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.22112605539976</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.81076019499452</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.22567741245846</v>
+        <v>34.11544574909353</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.33116880250356</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.23396827838354</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.27648996376357</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.11885207074495</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.15173688753096</v>
       </c>
     </row>
   </sheetData>
@@ -12423,22 +12423,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.71649768880367</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.05889988678796</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.03892107548378</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.47371831235974</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.64146425181982</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.06130805074894</v>
+        <v>39.02001940958394</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.41812001630416</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.5943799168837</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.88898507455924</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.6627761247041</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.95422739910344</v>
       </c>
     </row>
   </sheetData>
@@ -12497,22 +12497,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.0970075662066</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.05598747650173</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.35481808686839</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.78826046759492</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.93926566073196</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.74424090632055</v>
+        <v>28.95908062871903</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.39214076564308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.90631619000245</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.77209690481553</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.80808170619675</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.22039138393578</v>
       </c>
     </row>
   </sheetData>
@@ -12571,22 +12571,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.13422778970746</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.41690668761825</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.53976067112328</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.91870234031424</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.91021371835173</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.78050679666688</v>
+        <v>36.05338764548511</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.98824162991772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.64867731854121</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.40471281333228</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.63017151704621</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.33675014926231</v>
       </c>
     </row>
   </sheetData>
@@ -12645,22 +12645,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.01099503285853</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.88390854382852</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.26658284590045</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.20752350422527</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.90311685517932</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.41378392354125</v>
+        <v>31.428573837217</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.94482207334232</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.67699814784234</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.78802127908184</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.46929482275366</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.35150279751468</v>
       </c>
     </row>
   </sheetData>
@@ -12719,22 +12719,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.35842954642631</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.5095513391906</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.69981719035651</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.94300539847909</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.37985871266502</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.16209680724803</v>
+        <v>28.19943388636253</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.4889181989063</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.62852501935556</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.53675235027007</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.05940437898062</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.70295316233395</v>
       </c>
     </row>
   </sheetData>
@@ -12793,22 +12793,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.55373682192764</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.255376744054</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.30074288333709</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.57886424319553</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.29065907158419</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.2731717075064</v>
+        <v>35.70040026759104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.8358878463044</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.9846452229301</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.83513764410756</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.69386425955775</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.04867590421837</v>
       </c>
     </row>
   </sheetData>
@@ -12867,22 +12867,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.14060194129406</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.03483820478828</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.0929387571197</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.89484454640306</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.24748529326973</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.23441967192154</v>
+        <v>32.91492039773932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.82742317294269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.5500924904523</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.08973368935701</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.44920135726134</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.41326158477409</v>
       </c>
     </row>
   </sheetData>
@@ -12941,22 +12941,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.71770504541749</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.16333650195171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.12086710451776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.53511465605893</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.96564560400911</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.82848486740529</v>
+        <v>26.63528988650166</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.09131216975842</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.91430998422661</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.65851535641038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.69321845666658</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.09484455096195</v>
       </c>
     </row>
   </sheetData>
@@ -13015,22 +13015,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.17274704545174</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.42049291557644</v>
-      </c>
-      <c r="D2" t="n">
-        <v>56.03611122519111</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.93734685263603</v>
-      </c>
-      <c r="F2" t="n">
-        <v>48.66688439478448</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.09308024662533</v>
+        <v>29.23878548355624</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.65897020230164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.90720067860234</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.70072193796921</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.3809500729945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.83963029847853</v>
       </c>
     </row>
   </sheetData>
@@ -13089,22 +13089,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.0566245650536</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.35778926668433</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.23347480783849</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.61862272640489</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.47213288668302</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.54979230676096</v>
+        <v>27.66938233779042</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.03723999898183</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.04401432939814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.41302176108219</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.09820149919437</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.93395937623859</v>
       </c>
     </row>
   </sheetData>
@@ -13163,22 +13163,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.52634671767028</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.95646727635999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.97393450809597</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.75622212879648</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.17595997158869</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.4457065606034</v>
+        <v>32.24006243071386</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.18482875813561</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.38336146276996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.8086008106624</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.30919440241582</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.13808144927939</v>
       </c>
     </row>
   </sheetData>
@@ -13237,22 +13237,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.21329689265695</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.69005595934311</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.94341106044821</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.18051836550362</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.84791278313011</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.2616292948972</v>
+        <v>34.60594506504805</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.73751657782103</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.78373357448306</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.27842419451532</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.00574652662381</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.56761991827953</v>
       </c>
     </row>
   </sheetData>
@@ -13311,22 +13311,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.99148898450356</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.61150853697844</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.76230346214115</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.79413459153526</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.81790790177153</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.3962298465638</v>
+        <v>32.12747089806069</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.28771837109365</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.82008772528971</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.73402848924981</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.62434387094729</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.14368746926691</v>
       </c>
     </row>
   </sheetData>
@@ -13385,22 +13385,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.04134997495652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.49388412579829</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.44027244859033</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.56109444221283</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.0186130924811</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.0510435118772</v>
+        <v>35.44340909467917</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.59769785851172</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.48217022617634</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.57895453599217</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.07092497714376</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.59473593038341</v>
       </c>
     </row>
   </sheetData>
@@ -13459,22 +13459,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.85588732346753</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.23929364666033</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.22919621268719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.82230923958443</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.31354478840924</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.92002694467894</v>
+        <v>33.62660233213164</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.9567153195149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.26153181417845</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.00206253566028</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.87236516045601</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.23712185940128</v>
       </c>
     </row>
   </sheetData>
@@ -13533,22 +13533,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.32694075929734</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.62286017182845</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.88070125255734</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.17749693460592</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.69172607593577</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.99178319344279</v>
+        <v>33.7852584271733</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.47649963167743</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.45874721338082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.81659971196745</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.3096789228685</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.72949722512908</v>
       </c>
     </row>
   </sheetData>
@@ -13607,22 +13607,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.7838619523486</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.64942522373008</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.42941154051761</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.95627127591154</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.57310961225217</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.0100587830335</v>
+        <v>27.92964146854586</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.75671055307804</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.81793579228838</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.94181517244936</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.91502145840979</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.22241420382626</v>
       </c>
     </row>
   </sheetData>
@@ -13681,22 +13681,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.72829860514662</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.02993601239107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.75884466227637</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.58993676545353</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.53959905283056</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.92180633597417</v>
+        <v>38.51491983030671</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.01878907355072</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.81626521733683</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.96202678094848</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.13011549482709</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.80008748940355</v>
       </c>
     </row>
   </sheetData>
@@ -13755,22 +13755,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.58069026626948</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.85919782634582</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.19831867861593</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.01748881076946</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.8466333943819</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.33319420163704</v>
+        <v>48.31462616801345</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.0536674536573</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.69032859772507</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.4013531239808</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.87860472488317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.95975949638884</v>
       </c>
     </row>
   </sheetData>
@@ -13829,22 +13829,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.80362038537186</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.76099058520791</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.21390543557236</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.00706382750381</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.81895305213356</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.20501422801143</v>
+        <v>40.1771669303693</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.01489008263577</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.8904691585183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.89342782053334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.0223546377601</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.90098964493867</v>
       </c>
     </row>
   </sheetData>
@@ -13903,22 +13903,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.62362506385556</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.09229522351441</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.95763795700824</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.30592904535539</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.97885764336108</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.43483410988102</v>
+        <v>29.05461087663486</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.18157254455995</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.64792584660126</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.77417195904816</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.13132717239739</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.89673737951209</v>
       </c>
     </row>
   </sheetData>
@@ -13977,22 +13977,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.62549088269482</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.4406974203449</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.34057719495185</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.57381010527217</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.05516425198065</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.45493106024122</v>
+        <v>36.87513514838026</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.25102845771251</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.41738278029852</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.25558816509841</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.59057895052453</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.9241145707681</v>
       </c>
     </row>
   </sheetData>
@@ -14051,22 +14051,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.58567759210592</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.66857815441044</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.34771667664893</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.5845378243153</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.01178809038377</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.59128577818097</v>
+        <v>37.6205398804554</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.51506109161949</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.35678660620422</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.57359567605672</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.5796427842216</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.39501296214721</v>
       </c>
     </row>
   </sheetData>
@@ -14125,22 +14125,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.33297547222325</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.6216917272872</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50.64065331977852</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.01616160768117</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.17388880075978</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.54094115987603</v>
+        <v>40.88449633615146</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.01422715278088</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.29321330437683</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.44827365062595</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.77857984789995</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.47769817679572</v>
       </c>
     </row>
   </sheetData>
@@ -14199,22 +14199,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.31340925253087</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.09283896603399</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.59338609163369</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.04214955275437</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.41211668832251</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.21226265634814</v>
+        <v>40.65849451254243</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.34751689074395</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.17436158881274</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.84836180015197</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.61587610305143</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.33413951348445</v>
       </c>
     </row>
   </sheetData>
@@ -14273,22 +14273,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.1500963009754</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.00449457109785</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.21798682375974</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.79968484491643</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.08765463991217</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.37800728904443</v>
+        <v>51.40886645067129</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.18452057898036</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.00703567273482</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.07711088885999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.41423386775081</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.83540892979318</v>
       </c>
     </row>
   </sheetData>
@@ -14347,22 +14347,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.30255433656854</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.59685932239951</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.72959129425723</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.95202354293668</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.65846695598354</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.65288189886855</v>
+        <v>26.32634214309166</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.62009210315455</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.41043482117861</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.42276634696398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.93923421596263</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.95126182375461</v>
       </c>
     </row>
   </sheetData>
@@ -14421,22 +14421,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.4826479702162</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.07485789370903</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.73621889683547</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.58984588928832</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.33905011607959</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.04637084856369</v>
+        <v>32.91795245364655</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.18649782066002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.76222124789701</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.02756162844846</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.13267740625959</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.99624661594644</v>
       </c>
     </row>
   </sheetData>
@@ -14495,22 +14495,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.29424104445053</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.8472069471223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.80185272113589</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.53969670372538</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.77539539027855</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.293186330644</v>
+        <v>33.8723620878923</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.18283940379881</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.58592436528039</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.94535242979581</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.65143384401504</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.99531713277581</v>
       </c>
     </row>
   </sheetData>
@@ -14569,22 +14569,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.22564094309667</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.49643544845352</v>
-      </c>
-      <c r="D2" t="n">
-        <v>52.03859044097959</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.62462082972319</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.77503078296877</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.57927004536857</v>
+        <v>41.22257642550721</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.6994341977387</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.56821078249923</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.30226523362482</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.40793013563827</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.29355357159667</v>
       </c>
     </row>
   </sheetData>
@@ -14643,22 +14643,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.27569941803414</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.66978982719779</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.48248085773149</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.87215053449764</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.59493153056955</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.45529164446614</v>
+        <v>53.43694091737981</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.41584077856455</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.7232923508824</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.88886127882924</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.45476351535173</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.09913187937107</v>
       </c>
     </row>
   </sheetData>
@@ -14717,22 +14717,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.40727660122112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.43840537089075</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.48763094355425</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.93673482311246</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.20434136367935</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.81572527433697</v>
+        <v>28.12595579831181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.44654797425489</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.53268544682376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.55199055466057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.46020120803514</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.58334342187608</v>
       </c>
     </row>
   </sheetData>
@@ -14791,22 +14791,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.99579217121108</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.68993376465794</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.18159794738544</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.71217854767833</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.01293127148082</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.41157686320279</v>
+        <v>34.44246083387353</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.50306231849751</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.20425380583177</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.78072745478779</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.60929907157986</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.14923827487367</v>
       </c>
     </row>
   </sheetData>
@@ -14865,22 +14865,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.98080005739813</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.13033011853653</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.52964297881972</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.43554041888212</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.27725747794693</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.59459656679362</v>
+        <v>29.86388310083947</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.07712126715601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.14592368214408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.80324648475041</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.94460043979488</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.38936225940183</v>
       </c>
     </row>
   </sheetData>
@@ -14939,22 +14939,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.88516625703364</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.70968227065126</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.70780676655242</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.78566946675302</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.87566712758243</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.6448562091316</v>
+        <v>25.27292981149747</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.77883048600316</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.65617751169323</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.88010043339995</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.88224039256921</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.34294169811029</v>
       </c>
     </row>
   </sheetData>
@@ -15013,22 +15013,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.32092948130849</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.53507348873999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.82633358103489</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.74085466379358</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.78631532844106</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.4253988199011</v>
+        <v>27.84678411370367</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.91018981841281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.44464097173755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.60333867961555</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.67812096225866</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.90534707053603</v>
       </c>
     </row>
   </sheetData>
@@ -15087,22 +15087,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.66999920938495</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.86936310058053</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.27915519700137</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.6440280083622</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.47513760640495</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.55279575401312</v>
+        <v>50.78287516943983</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.20179434551245</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.29690011239563</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.79366170452022</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.59895101497919</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.01415962637145</v>
       </c>
     </row>
   </sheetData>
@@ -15161,22 +15161,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.66760321915982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.80413123603264</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.47200367983376</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.95167592163028</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.66356046951181</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.36261680951988</v>
+        <v>34.02932467687451</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.29375906217422</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.59150375421049</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.00860130570913</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.7750872444947</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.71892115491561</v>
       </c>
     </row>
   </sheetData>
@@ -15235,22 +15235,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.08991966807111</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.58895382347108</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.48454348402051</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.7602005325232</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.6517386512127</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.6594679948776</v>
+        <v>28.99166641861652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.8976169035903</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.80844716979868</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.87257208248042</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.77119043160361</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.71268357217942</v>
       </c>
     </row>
   </sheetData>
@@ -15309,22 +15309,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.27562466083552</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.03575269984161</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.1460103824018</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.42508362074503</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.4238379356028</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.46329813046668</v>
+        <v>27.02194589415862</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.59616801979529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.63644161053175</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.78129513534735</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.41506795785266</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.51121623348878</v>
       </c>
     </row>
   </sheetData>
@@ -15383,22 +15383,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.09001826330643</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.86212556848598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.64792028562923</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.3826713164006</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.94851367536678</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.11416045530281</v>
+        <v>29.95062806177439</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.17619040857284</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.49388234400187</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.8682662241343</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.62776307194296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.25024834301508</v>
       </c>
     </row>
   </sheetData>
